--- a/Stock_OneClick/history/scan_result_20260602_130123.xlsx
+++ b/Stock_OneClick/history/scan_result_20260602_130123.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q217"/>
+  <dimension ref="A1:Q216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -666,24 +666,12 @@
       <c r="J3" s="4" t="n">
         <v>187.24</v>
       </c>
-      <c r="K3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-06-02; 相对D0=11.87%; 本次触发=2026-06-02(正式买入 | 预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02</t>
@@ -735,24 +723,12 @@
       <c r="J4" s="4" t="n">
         <v>48.67</v>
       </c>
-      <c r="K4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-06-02; 相对D0=1.14%; 本次触发=2026-06-02(正式买入 | 预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02</t>
@@ -804,24 +780,12 @@
       <c r="J5" s="4" t="n">
         <v>142.92</v>
       </c>
-      <c r="K5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>D0=135.28; 最新=2026-06-02; 相对D0=5.65%; 本次触发=2026-06-02(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-02</t>
@@ -873,24 +837,12 @@
       <c r="J6" s="4" t="n">
         <v>138.63</v>
       </c>
-      <c r="K6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-06-02; 相对D0=-1.83%; 本次触发=2026-06-02(正式买入); 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -942,24 +894,12 @@
       <c r="J7" s="4" t="n">
         <v>417.88</v>
       </c>
-      <c r="K7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
+      <c r="P7" s="4" t="n"/>
       <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-06-02; 相对D0=6.78%; 本次触发=2026-06-02(预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -1011,24 +951,6 @@
       <c r="J8" t="n">
         <v>23.305</v>
       </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-06-02; 相对D0=3.53%; 本次触发=2026-06-02(预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -1080,24 +1002,12 @@
       <c r="J9" s="4" t="n">
         <v>133.52</v>
       </c>
-      <c r="K9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>D0=137.65; 最新=2026-06-02; 相对D0=-3.00%; 本次触发=2026-06-02(预警买入); 历史重复1次; 重复日期=2026-06-02</t>
@@ -1149,24 +1059,12 @@
       <c r="J10" s="4" t="n">
         <v>278.01</v>
       </c>
-      <c r="K10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P10" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
+      <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-06-02; 相对D0=6.01%; 本次触发=2026-06-02(正式买入 | 预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-05-27, 2026-06-02</t>
@@ -1218,24 +1116,6 @@
       <c r="J11" t="n">
         <v>56.89</v>
       </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>D0=54.94; 最新=2026-06-02; 相对D0=3.55%; 本次触发=2026-06-02(预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -1287,24 +1167,6 @@
       <c r="J12" t="n">
         <v>87.39</v>
       </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>D0=81.76; 最新=2026-06-02; 相对D0=6.89%; 本次触发=2026-06-02(预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -1356,24 +1218,12 @@
       <c r="J13" s="4" t="n">
         <v>15.445</v>
       </c>
-      <c r="K13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-06-02; 相对D0=18.63%; 本次触发=2026-06-02(正式买入 | 预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02</t>
@@ -1425,24 +1275,12 @@
       <c r="J14" s="4" t="n">
         <v>157.97</v>
       </c>
-      <c r="K14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>D0=156.27; 最新=2026-06-02; 相对D0=1.09%; 本次触发=2026-06-02(预警买入); 历史重复1次; 重复日期=2026-06-02</t>
@@ -1494,24 +1332,6 @@
       <c r="J15" t="n">
         <v>51.51</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=50.29; 最新=2026-06-02; 相对D0=2.43%; 本次触发=2026-06-02(预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -1563,24 +1383,12 @@
       <c r="J16" s="4" t="n">
         <v>137.91</v>
       </c>
-      <c r="K16" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N16" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O16" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P16" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="4" t="n"/>
+      <c r="P16" s="4" t="n"/>
       <c r="Q16" s="4" t="inlineStr">
         <is>
           <t>D0=134.61; 最新=2026-06-02; 相对D0=2.45%; 本次触发=2026-06-02(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-28, 2026-06-02</t>
@@ -1632,24 +1440,12 @@
       <c r="J17" s="4" t="n">
         <v>73.48</v>
       </c>
-      <c r="K17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P17" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
+      <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>D0=68.70; 最新=2026-06-02; 相对D0=6.96%; 本次触发=2026-06-02(预警买入); 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -1701,27 +1497,15 @@
       <c r="J18" s="4" t="n">
         <v>19.52</v>
       </c>
-      <c r="K18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t>D0=18.40; 最新=2026-06-02; 相对D0=6.09%; 本次触发=2026-06-02(正式买入 | 第一买入点 | 预警买入); 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
+          <t>D0=18.40; 最新=2026-06-02; 相对D0=6.09%; 本次触发=2026-06-02(正式买入 | 第一观察点 | 预警买入); 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
         </is>
       </c>
     </row>
@@ -1770,27 +1554,9 @@
       <c r="J19" t="n">
         <v>334.5945</v>
       </c>
-      <c r="K19" t="n">
-        <v/>
-      </c>
-      <c r="L19" t="n">
-        <v/>
-      </c>
-      <c r="M19" t="n">
-        <v/>
-      </c>
-      <c r="N19" t="n">
-        <v/>
-      </c>
-      <c r="O19" t="n">
-        <v/>
-      </c>
-      <c r="P19" t="n">
-        <v/>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>D0=323.91; 最新=2026-06-02; 相对D0=3.30%; 本次触发=2026-06-02(正式买入 | 第一买入点); 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
+          <t>D0=323.91; 最新=2026-06-02; 相对D0=3.30%; 本次触发=2026-06-02(正式买入 | 第一观察点); 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
         </is>
       </c>
     </row>
@@ -1839,24 +1605,6 @@
       <c r="J20" t="n">
         <v>303.1</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=290.01; 最新=2026-06-02; 相对D0=4.51%; 本次触发=2026-06-02(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-02</t>
@@ -1908,24 +1656,6 @@
       <c r="J21" t="n">
         <v>66.45</v>
       </c>
-      <c r="K21" t="n">
-        <v/>
-      </c>
-      <c r="L21" t="n">
-        <v/>
-      </c>
-      <c r="M21" t="n">
-        <v/>
-      </c>
-      <c r="N21" t="n">
-        <v/>
-      </c>
-      <c r="O21" t="n">
-        <v/>
-      </c>
-      <c r="P21" t="n">
-        <v/>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>D0=67.38; 最新=2026-06-02; 相对D0=-1.38%; 本次触发=2026-06-02(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-02</t>
@@ -1977,24 +1707,12 @@
       <c r="J22" s="4" t="n">
         <v>392.26</v>
       </c>
-      <c r="K22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P22" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="4" t="n"/>
+      <c r="N22" s="4" t="n"/>
+      <c r="O22" s="4" t="n"/>
+      <c r="P22" s="4" t="n"/>
       <c r="Q22" s="4" t="inlineStr">
         <is>
           <t>D0=374.31; 最新=2026-06-02; 相对D0=4.80%; 本次触发=2026-06-02(预警买入); 历史重复1次; 重复日期=2026-06-02</t>
@@ -2046,24 +1764,12 @@
       <c r="J23" s="4" t="n">
         <v>116.87</v>
       </c>
-      <c r="K23" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M23" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N23" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O23" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P23" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="4" t="n"/>
+      <c r="O23" s="4" t="n"/>
+      <c r="P23" s="4" t="n"/>
       <c r="Q23" s="4" t="inlineStr">
         <is>
           <t>D0=115.58; 最新=2026-06-02; 相对D0=1.12%; 本次触发=2026-06-02(预警买入); 历史重复1次; 重复日期=2026-06-02</t>
@@ -2115,24 +1821,12 @@
       <c r="J24" s="4" t="n">
         <v>187.63</v>
       </c>
-      <c r="K24" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O24" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P24" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="4" t="n"/>
+      <c r="O24" s="4" t="n"/>
+      <c r="P24" s="4" t="n"/>
       <c r="Q24" s="4" t="inlineStr">
         <is>
           <t>D0=185.83; 最新=2026-06-02; 相对D0=0.97%; 本次触发=2026-06-02(正式买入); 历史重复1次; 重复日期=2026-06-02</t>
@@ -2184,24 +1878,6 @@
       <c r="J25" t="n">
         <v>12.72</v>
       </c>
-      <c r="K25" t="n">
-        <v/>
-      </c>
-      <c r="L25" t="n">
-        <v/>
-      </c>
-      <c r="M25" t="n">
-        <v/>
-      </c>
-      <c r="N25" t="n">
-        <v/>
-      </c>
-      <c r="O25" t="n">
-        <v/>
-      </c>
-      <c r="P25" t="n">
-        <v/>
-      </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>D0=11.02; 最新=2026-06-02; 相对D0=15.43%; 本次触发=2026-06-02(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-02</t>
@@ -2253,24 +1929,6 @@
       <c r="J26" t="n">
         <v>315.2</v>
       </c>
-      <c r="K26" t="n">
-        <v/>
-      </c>
-      <c r="L26" t="n">
-        <v/>
-      </c>
-      <c r="M26" t="n">
-        <v/>
-      </c>
-      <c r="N26" t="n">
-        <v/>
-      </c>
-      <c r="O26" t="n">
-        <v/>
-      </c>
-      <c r="P26" t="n">
-        <v/>
-      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>D0=315.20; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -2322,24 +1980,12 @@
       <c r="J27" s="4" t="n">
         <v>113</v>
       </c>
-      <c r="K27" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L27" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M27" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N27" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O27" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P27" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="n"/>
+      <c r="O27" s="4" t="n"/>
+      <c r="P27" s="4" t="n"/>
       <c r="Q27" s="4" t="inlineStr">
         <is>
           <t>D0=113.00; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -2391,24 +2037,6 @@
       <c r="J28" t="n">
         <v>118.17</v>
       </c>
-      <c r="K28" t="n">
-        <v/>
-      </c>
-      <c r="L28" t="n">
-        <v/>
-      </c>
-      <c r="M28" t="n">
-        <v/>
-      </c>
-      <c r="N28" t="n">
-        <v/>
-      </c>
-      <c r="O28" t="n">
-        <v/>
-      </c>
-      <c r="P28" t="n">
-        <v/>
-      </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>D0=118.17; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -2460,24 +2088,6 @@
       <c r="J29" t="n">
         <v>303.1</v>
       </c>
-      <c r="K29" t="n">
-        <v/>
-      </c>
-      <c r="L29" t="n">
-        <v/>
-      </c>
-      <c r="M29" t="n">
-        <v/>
-      </c>
-      <c r="N29" t="n">
-        <v/>
-      </c>
-      <c r="O29" t="n">
-        <v/>
-      </c>
-      <c r="P29" t="n">
-        <v/>
-      </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>D0=303.10; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -2529,24 +2139,12 @@
       <c r="J30" s="4" t="n">
         <v>187.24</v>
       </c>
-      <c r="K30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P30" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="n"/>
+      <c r="N30" s="4" t="n"/>
+      <c r="O30" s="4" t="n"/>
+      <c r="P30" s="4" t="n"/>
       <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>D0=187.24; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -2598,24 +2196,6 @@
       <c r="J31" t="n">
         <v>426.89</v>
       </c>
-      <c r="K31" t="n">
-        <v/>
-      </c>
-      <c r="L31" t="n">
-        <v/>
-      </c>
-      <c r="M31" t="n">
-        <v/>
-      </c>
-      <c r="N31" t="n">
-        <v/>
-      </c>
-      <c r="O31" t="n">
-        <v/>
-      </c>
-      <c r="P31" t="n">
-        <v/>
-      </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>D0=426.89; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -2667,24 +2247,12 @@
       <c r="J32" s="4" t="n">
         <v>116.87</v>
       </c>
-      <c r="K32" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L32" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M32" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N32" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O32" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P32" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="n"/>
+      <c r="N32" s="4" t="n"/>
+      <c r="O32" s="4" t="n"/>
+      <c r="P32" s="4" t="n"/>
       <c r="Q32" s="4" t="inlineStr">
         <is>
           <t>D0=116.87; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -2736,24 +2304,6 @@
       <c r="J33" t="n">
         <v>229</v>
       </c>
-      <c r="K33" t="n">
-        <v/>
-      </c>
-      <c r="L33" t="n">
-        <v/>
-      </c>
-      <c r="M33" t="n">
-        <v/>
-      </c>
-      <c r="N33" t="n">
-        <v/>
-      </c>
-      <c r="O33" t="n">
-        <v/>
-      </c>
-      <c r="P33" t="n">
-        <v/>
-      </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>D0=229.00; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -2805,24 +2355,12 @@
       <c r="J34" s="4" t="n">
         <v>187.63</v>
       </c>
-      <c r="K34" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L34" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M34" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N34" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O34" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P34" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
+      <c r="M34" s="4" t="n"/>
+      <c r="N34" s="4" t="n"/>
+      <c r="O34" s="4" t="n"/>
+      <c r="P34" s="4" t="n"/>
       <c r="Q34" s="4" t="inlineStr">
         <is>
           <t>D0=187.63; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入)</t>
@@ -2874,24 +2412,6 @@
       <c r="J35" t="n">
         <v>66.45</v>
       </c>
-      <c r="K35" t="n">
-        <v/>
-      </c>
-      <c r="L35" t="n">
-        <v/>
-      </c>
-      <c r="M35" t="n">
-        <v/>
-      </c>
-      <c r="N35" t="n">
-        <v/>
-      </c>
-      <c r="O35" t="n">
-        <v/>
-      </c>
-      <c r="P35" t="n">
-        <v/>
-      </c>
       <c r="Q35" t="inlineStr">
         <is>
           <t>D0=66.45; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -2943,24 +2463,12 @@
       <c r="J36" s="4" t="n">
         <v>48.67</v>
       </c>
-      <c r="K36" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L36" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M36" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N36" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O36" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P36" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K36" s="4" t="n"/>
+      <c r="L36" s="4" t="n"/>
+      <c r="M36" s="4" t="n"/>
+      <c r="N36" s="4" t="n"/>
+      <c r="O36" s="4" t="n"/>
+      <c r="P36" s="4" t="n"/>
       <c r="Q36" s="4" t="inlineStr">
         <is>
           <t>D0=48.67; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -3012,24 +2520,6 @@
       <c r="J37" t="n">
         <v>72.33</v>
       </c>
-      <c r="K37" t="n">
-        <v/>
-      </c>
-      <c r="L37" t="n">
-        <v/>
-      </c>
-      <c r="M37" t="n">
-        <v/>
-      </c>
-      <c r="N37" t="n">
-        <v/>
-      </c>
-      <c r="O37" t="n">
-        <v/>
-      </c>
-      <c r="P37" t="n">
-        <v/>
-      </c>
       <c r="Q37" t="inlineStr">
         <is>
           <t>D0=72.33; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -3081,24 +2571,12 @@
       <c r="J38" s="4" t="n">
         <v>142.92</v>
       </c>
-      <c r="K38" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L38" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M38" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N38" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O38" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P38" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K38" s="4" t="n"/>
+      <c r="L38" s="4" t="n"/>
+      <c r="M38" s="4" t="n"/>
+      <c r="N38" s="4" t="n"/>
+      <c r="O38" s="4" t="n"/>
+      <c r="P38" s="4" t="n"/>
       <c r="Q38" s="4" t="inlineStr">
         <is>
           <t>D0=142.92; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -3150,24 +2628,12 @@
       <c r="J39" s="4" t="n">
         <v>138.63</v>
       </c>
-      <c r="K39" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L39" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M39" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N39" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O39" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P39" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K39" s="4" t="n"/>
+      <c r="L39" s="4" t="n"/>
+      <c r="M39" s="4" t="n"/>
+      <c r="N39" s="4" t="n"/>
+      <c r="O39" s="4" t="n"/>
+      <c r="P39" s="4" t="n"/>
       <c r="Q39" s="4" t="inlineStr">
         <is>
           <t>D0=138.63; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入)</t>
@@ -3219,24 +2685,12 @@
       <c r="J40" s="4" t="n">
         <v>417.88</v>
       </c>
-      <c r="K40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P40" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K40" s="4" t="n"/>
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="4" t="n"/>
+      <c r="N40" s="4" t="n"/>
+      <c r="O40" s="4" t="n"/>
+      <c r="P40" s="4" t="n"/>
       <c r="Q40" s="4" t="inlineStr">
         <is>
           <t>D0=417.88; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -3288,24 +2742,6 @@
       <c r="J41" t="n">
         <v>200.4</v>
       </c>
-      <c r="K41" t="n">
-        <v/>
-      </c>
-      <c r="L41" t="n">
-        <v/>
-      </c>
-      <c r="M41" t="n">
-        <v/>
-      </c>
-      <c r="N41" t="n">
-        <v/>
-      </c>
-      <c r="O41" t="n">
-        <v/>
-      </c>
-      <c r="P41" t="n">
-        <v/>
-      </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>D0=200.40; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -3357,24 +2793,12 @@
       <c r="J42" s="4" t="n">
         <v>40.12</v>
       </c>
-      <c r="K42" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L42" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M42" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N42" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O42" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P42" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K42" s="4" t="n"/>
+      <c r="L42" s="4" t="n"/>
+      <c r="M42" s="4" t="n"/>
+      <c r="N42" s="4" t="n"/>
+      <c r="O42" s="4" t="n"/>
+      <c r="P42" s="4" t="n"/>
       <c r="Q42" s="4" t="inlineStr">
         <is>
           <t>D0=40.12; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -3426,24 +2850,6 @@
       <c r="J43" t="n">
         <v>12.72</v>
       </c>
-      <c r="K43" t="n">
-        <v/>
-      </c>
-      <c r="L43" t="n">
-        <v/>
-      </c>
-      <c r="M43" t="n">
-        <v/>
-      </c>
-      <c r="N43" t="n">
-        <v/>
-      </c>
-      <c r="O43" t="n">
-        <v/>
-      </c>
-      <c r="P43" t="n">
-        <v/>
-      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>D0=12.72; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -3495,24 +2901,6 @@
       <c r="J44" t="n">
         <v>11.7</v>
       </c>
-      <c r="K44" t="n">
-        <v/>
-      </c>
-      <c r="L44" t="n">
-        <v/>
-      </c>
-      <c r="M44" t="n">
-        <v/>
-      </c>
-      <c r="N44" t="n">
-        <v/>
-      </c>
-      <c r="O44" t="n">
-        <v/>
-      </c>
-      <c r="P44" t="n">
-        <v/>
-      </c>
       <c r="Q44" t="inlineStr">
         <is>
           <t>D0=11.70; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -3564,24 +2952,6 @@
       <c r="J45" t="n">
         <v>23.305</v>
       </c>
-      <c r="K45" t="n">
-        <v/>
-      </c>
-      <c r="L45" t="n">
-        <v/>
-      </c>
-      <c r="M45" t="n">
-        <v/>
-      </c>
-      <c r="N45" t="n">
-        <v/>
-      </c>
-      <c r="O45" t="n">
-        <v/>
-      </c>
-      <c r="P45" t="n">
-        <v/>
-      </c>
       <c r="Q45" t="inlineStr">
         <is>
           <t>D0=23.30; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -3633,24 +3003,12 @@
       <c r="J46" s="4" t="n">
         <v>137.91</v>
       </c>
-      <c r="K46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P46" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n"/>
+      <c r="N46" s="4" t="n"/>
+      <c r="O46" s="4" t="n"/>
+      <c r="P46" s="4" t="n"/>
       <c r="Q46" s="4" t="inlineStr">
         <is>
           <t>D0=137.91; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -3702,24 +3060,12 @@
       <c r="J47" s="4" t="n">
         <v>133.52</v>
       </c>
-      <c r="K47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P47" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K47" s="4" t="n"/>
+      <c r="L47" s="4" t="n"/>
+      <c r="M47" s="4" t="n"/>
+      <c r="N47" s="4" t="n"/>
+      <c r="O47" s="4" t="n"/>
+      <c r="P47" s="4" t="n"/>
       <c r="Q47" s="4" t="inlineStr">
         <is>
           <t>D0=133.52; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -3771,24 +3117,12 @@
       <c r="J48" s="4" t="n">
         <v>25.86</v>
       </c>
-      <c r="K48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P48" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K48" s="4" t="n"/>
+      <c r="L48" s="4" t="n"/>
+      <c r="M48" s="4" t="n"/>
+      <c r="N48" s="4" t="n"/>
+      <c r="O48" s="4" t="n"/>
+      <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="inlineStr">
         <is>
           <t>D0=25.86; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入)</t>
@@ -3840,24 +3174,12 @@
       <c r="J49" s="4" t="n">
         <v>73.48</v>
       </c>
-      <c r="K49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P49" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="n"/>
+      <c r="M49" s="4" t="n"/>
+      <c r="N49" s="4" t="n"/>
+      <c r="O49" s="4" t="n"/>
+      <c r="P49" s="4" t="n"/>
       <c r="Q49" s="4" t="inlineStr">
         <is>
           <t>D0=73.48; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -3909,24 +3231,12 @@
       <c r="J50" s="4" t="n">
         <v>278.01</v>
       </c>
-      <c r="K50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P50" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="n"/>
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="4" t="n"/>
+      <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="inlineStr">
         <is>
           <t>D0=278.01; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -3978,24 +3288,6 @@
       <c r="J51" t="n">
         <v>56.89</v>
       </c>
-      <c r="K51" t="n">
-        <v/>
-      </c>
-      <c r="L51" t="n">
-        <v/>
-      </c>
-      <c r="M51" t="n">
-        <v/>
-      </c>
-      <c r="N51" t="n">
-        <v/>
-      </c>
-      <c r="O51" t="n">
-        <v/>
-      </c>
-      <c r="P51" t="n">
-        <v/>
-      </c>
       <c r="Q51" t="inlineStr">
         <is>
           <t>D0=56.89; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -4047,24 +3339,12 @@
       <c r="J52" s="4" t="n">
         <v>56.57</v>
       </c>
-      <c r="K52" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L52" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M52" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N52" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O52" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P52" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K52" s="4" t="n"/>
+      <c r="L52" s="4" t="n"/>
+      <c r="M52" s="4" t="n"/>
+      <c r="N52" s="4" t="n"/>
+      <c r="O52" s="4" t="n"/>
+      <c r="P52" s="4" t="n"/>
       <c r="Q52" s="4" t="inlineStr">
         <is>
           <t>D0=56.57; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -4116,24 +3396,6 @@
       <c r="J53" t="n">
         <v>508.37</v>
       </c>
-      <c r="K53" t="n">
-        <v/>
-      </c>
-      <c r="L53" t="n">
-        <v/>
-      </c>
-      <c r="M53" t="n">
-        <v/>
-      </c>
-      <c r="N53" t="n">
-        <v/>
-      </c>
-      <c r="O53" t="n">
-        <v/>
-      </c>
-      <c r="P53" t="n">
-        <v/>
-      </c>
       <c r="Q53" t="inlineStr">
         <is>
           <t>D0=508.37; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -4185,24 +3447,6 @@
       <c r="J54" t="n">
         <v>87.39</v>
       </c>
-      <c r="K54" t="n">
-        <v/>
-      </c>
-      <c r="L54" t="n">
-        <v/>
-      </c>
-      <c r="M54" t="n">
-        <v/>
-      </c>
-      <c r="N54" t="n">
-        <v/>
-      </c>
-      <c r="O54" t="n">
-        <v/>
-      </c>
-      <c r="P54" t="n">
-        <v/>
-      </c>
       <c r="Q54" t="inlineStr">
         <is>
           <t>D0=87.39; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -4254,24 +3498,12 @@
       <c r="J55" s="4" t="n">
         <v>392.26</v>
       </c>
-      <c r="K55" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L55" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M55" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N55" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O55" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P55" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K55" s="4" t="n"/>
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="4" t="n"/>
+      <c r="O55" s="4" t="n"/>
+      <c r="P55" s="4" t="n"/>
       <c r="Q55" s="4" t="inlineStr">
         <is>
           <t>D0=392.26; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -4323,24 +3555,12 @@
       <c r="J56" s="4" t="n">
         <v>385.51</v>
       </c>
-      <c r="K56" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L56" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M56" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N56" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O56" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P56" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K56" s="4" t="n"/>
+      <c r="L56" s="4" t="n"/>
+      <c r="M56" s="4" t="n"/>
+      <c r="N56" s="4" t="n"/>
+      <c r="O56" s="4" t="n"/>
+      <c r="P56" s="4" t="n"/>
       <c r="Q56" s="4" t="inlineStr">
         <is>
           <t>D0=385.51; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -4392,24 +3612,6 @@
       <c r="J57" t="n">
         <v>274.71</v>
       </c>
-      <c r="K57" t="n">
-        <v/>
-      </c>
-      <c r="L57" t="n">
-        <v/>
-      </c>
-      <c r="M57" t="n">
-        <v/>
-      </c>
-      <c r="N57" t="n">
-        <v/>
-      </c>
-      <c r="O57" t="n">
-        <v/>
-      </c>
-      <c r="P57" t="n">
-        <v/>
-      </c>
       <c r="Q57" t="inlineStr">
         <is>
           <t>D0=274.71; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -4461,24 +3663,12 @@
       <c r="J58" s="4" t="n">
         <v>15.445</v>
       </c>
-      <c r="K58" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L58" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M58" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N58" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O58" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P58" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K58" s="4" t="n"/>
+      <c r="L58" s="4" t="n"/>
+      <c r="M58" s="4" t="n"/>
+      <c r="N58" s="4" t="n"/>
+      <c r="O58" s="4" t="n"/>
+      <c r="P58" s="4" t="n"/>
       <c r="Q58" s="4" t="inlineStr">
         <is>
           <t>D0=15.45; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -4530,27 +3720,15 @@
       <c r="J59" s="4" t="n">
         <v>19.52</v>
       </c>
-      <c r="K59" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P59" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K59" s="4" t="n"/>
+      <c r="L59" s="4" t="n"/>
+      <c r="M59" s="4" t="n"/>
+      <c r="N59" s="4" t="n"/>
+      <c r="O59" s="4" t="n"/>
+      <c r="P59" s="4" t="n"/>
       <c r="Q59" s="4" t="inlineStr">
         <is>
-          <t>D0=19.52; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 第一买入点 | 预警买入)</t>
+          <t>D0=19.52; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 第一观察点 | 预警买入)</t>
         </is>
       </c>
     </row>
@@ -4599,27 +3777,9 @@
       <c r="J60" t="n">
         <v>334.5945</v>
       </c>
-      <c r="K60" t="n">
-        <v/>
-      </c>
-      <c r="L60" t="n">
-        <v/>
-      </c>
-      <c r="M60" t="n">
-        <v/>
-      </c>
-      <c r="N60" t="n">
-        <v/>
-      </c>
-      <c r="O60" t="n">
-        <v/>
-      </c>
-      <c r="P60" t="n">
-        <v/>
-      </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>D0=334.59; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 第一买入点)</t>
+          <t>D0=334.59; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 第一观察点)</t>
         </is>
       </c>
     </row>
@@ -4668,24 +3828,12 @@
       <c r="J61" s="4" t="n">
         <v>157.97</v>
       </c>
-      <c r="K61" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L61" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M61" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N61" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O61" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P61" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K61" s="4" t="n"/>
+      <c r="L61" s="4" t="n"/>
+      <c r="M61" s="4" t="n"/>
+      <c r="N61" s="4" t="n"/>
+      <c r="O61" s="4" t="n"/>
+      <c r="P61" s="4" t="n"/>
       <c r="Q61" s="4" t="inlineStr">
         <is>
           <t>D0=157.97; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -4737,24 +3885,6 @@
       <c r="J62" t="n">
         <v>51.51</v>
       </c>
-      <c r="K62" t="n">
-        <v/>
-      </c>
-      <c r="L62" t="n">
-        <v/>
-      </c>
-      <c r="M62" t="n">
-        <v/>
-      </c>
-      <c r="N62" t="n">
-        <v/>
-      </c>
-      <c r="O62" t="n">
-        <v/>
-      </c>
-      <c r="P62" t="n">
-        <v/>
-      </c>
       <c r="Q62" t="inlineStr">
         <is>
           <t>D0=51.51; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -4806,24 +3936,12 @@
       <c r="J63" s="4" t="n">
         <v>57.945</v>
       </c>
-      <c r="K63" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L63" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M63" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N63" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O63" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P63" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K63" s="4" t="n"/>
+      <c r="L63" s="4" t="n"/>
+      <c r="M63" s="4" t="n"/>
+      <c r="N63" s="4" t="n"/>
+      <c r="O63" s="4" t="n"/>
+      <c r="P63" s="4" t="n"/>
       <c r="Q63" s="4" t="inlineStr">
         <is>
           <t>D0=57.95; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -4875,24 +3993,6 @@
       <c r="J64" t="n">
         <v>202.37</v>
       </c>
-      <c r="K64" t="n">
-        <v/>
-      </c>
-      <c r="L64" t="n">
-        <v/>
-      </c>
-      <c r="M64" t="n">
-        <v/>
-      </c>
-      <c r="N64" t="n">
-        <v/>
-      </c>
-      <c r="O64" t="n">
-        <v/>
-      </c>
-      <c r="P64" t="n">
-        <v/>
-      </c>
       <c r="Q64" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-06-02; 相对D0=11.50%; 历史重复2次; 重复日期=2026-05-27, 2026-06-01</t>
@@ -4944,24 +4044,12 @@
       <c r="J65" s="4" t="n">
         <v>187.254</v>
       </c>
-      <c r="K65" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L65" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M65" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N65" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O65" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P65" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K65" s="4" t="n"/>
+      <c r="L65" s="4" t="n"/>
+      <c r="M65" s="4" t="n"/>
+      <c r="N65" s="4" t="n"/>
+      <c r="O65" s="4" t="n"/>
+      <c r="P65" s="4" t="n"/>
       <c r="Q65" s="4" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-06-02; 相对D0=-7.72%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -5013,24 +4101,12 @@
       <c r="J66" s="4" t="n">
         <v>272.65</v>
       </c>
-      <c r="K66" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L66" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M66" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N66" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O66" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P66" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K66" s="4" t="n"/>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="4" t="n"/>
+      <c r="N66" s="4" t="n"/>
+      <c r="O66" s="4" t="n"/>
+      <c r="P66" s="4" t="n"/>
       <c r="Q66" s="4" t="inlineStr">
         <is>
           <t>D0=294.07; 最新=2026-06-02; 相对D0=-7.28%; 历史重复1次; 重复日期=2026-05-29</t>
@@ -5082,24 +4158,12 @@
       <c r="J67" s="4" t="n">
         <v>57.59</v>
       </c>
-      <c r="K67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P67" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K67" s="4" t="n"/>
+      <c r="L67" s="4" t="n"/>
+      <c r="M67" s="4" t="n"/>
+      <c r="N67" s="4" t="n"/>
+      <c r="O67" s="4" t="n"/>
+      <c r="P67" s="4" t="n"/>
       <c r="Q67" s="4" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-06-02; 相对D0=23.77%</t>
@@ -5151,24 +4215,6 @@
       <c r="J68" t="n">
         <v>16.755</v>
       </c>
-      <c r="K68" t="n">
-        <v/>
-      </c>
-      <c r="L68" t="n">
-        <v/>
-      </c>
-      <c r="M68" t="n">
-        <v/>
-      </c>
-      <c r="N68" t="n">
-        <v/>
-      </c>
-      <c r="O68" t="n">
-        <v/>
-      </c>
-      <c r="P68" t="n">
-        <v/>
-      </c>
       <c r="Q68" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-06-02; 相对D0=3.94%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -5220,24 +4266,12 @@
       <c r="J69" s="4" t="n">
         <v>200.83</v>
       </c>
-      <c r="K69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P69" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K69" s="4" t="n"/>
+      <c r="L69" s="4" t="n"/>
+      <c r="M69" s="4" t="n"/>
+      <c r="N69" s="4" t="n"/>
+      <c r="O69" s="4" t="n"/>
+      <c r="P69" s="4" t="n"/>
       <c r="Q69" s="4" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-06-02; 相对D0=11.53%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -5289,24 +4323,12 @@
       <c r="J70" s="4" t="n">
         <v>969.62</v>
       </c>
-      <c r="K70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P70" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K70" s="4" t="n"/>
+      <c r="L70" s="4" t="n"/>
+      <c r="M70" s="4" t="n"/>
+      <c r="N70" s="4" t="n"/>
+      <c r="O70" s="4" t="n"/>
+      <c r="P70" s="4" t="n"/>
       <c r="Q70" s="4" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-06-02; 相对D0=-6.65%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -5358,24 +4380,6 @@
       <c r="J71" t="n">
         <v>49.93</v>
       </c>
-      <c r="K71" t="n">
-        <v/>
-      </c>
-      <c r="L71" t="n">
-        <v/>
-      </c>
-      <c r="M71" t="n">
-        <v/>
-      </c>
-      <c r="N71" t="n">
-        <v/>
-      </c>
-      <c r="O71" t="n">
-        <v/>
-      </c>
-      <c r="P71" t="n">
-        <v/>
-      </c>
       <c r="Q71" t="inlineStr">
         <is>
           <t>D0=50.66; 最新=2026-06-02; 相对D0=-1.44%; 历史重复2次; 重复日期=2026-05-27, 2026-06-01</t>
@@ -5427,24 +4431,12 @@
       <c r="J72" s="4" t="n">
         <v>199.12</v>
       </c>
-      <c r="K72" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L72" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M72" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N72" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O72" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P72" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K72" s="4" t="n"/>
+      <c r="L72" s="4" t="n"/>
+      <c r="M72" s="4" t="n"/>
+      <c r="N72" s="4" t="n"/>
+      <c r="O72" s="4" t="n"/>
+      <c r="P72" s="4" t="n"/>
       <c r="Q72" s="4" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-06-02; 相对D0=11.02%; 历史重复3次; 重复日期=2026-05-26, 2026-05-28, 2026-06-01</t>
@@ -5496,24 +4488,12 @@
       <c r="J73" s="4" t="n">
         <v>398.46</v>
       </c>
-      <c r="K73" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L73" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M73" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N73" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O73" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P73" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K73" s="4" t="n"/>
+      <c r="L73" s="4" t="n"/>
+      <c r="M73" s="4" t="n"/>
+      <c r="N73" s="4" t="n"/>
+      <c r="O73" s="4" t="n"/>
+      <c r="P73" s="4" t="n"/>
       <c r="Q73" s="4" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-06-02; 相对D0=22.18%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -5565,24 +4545,6 @@
       <c r="J74" t="n">
         <v>597.63</v>
       </c>
-      <c r="K74" t="n">
-        <v/>
-      </c>
-      <c r="L74" t="n">
-        <v/>
-      </c>
-      <c r="M74" t="n">
-        <v/>
-      </c>
-      <c r="N74" t="n">
-        <v/>
-      </c>
-      <c r="O74" t="n">
-        <v/>
-      </c>
-      <c r="P74" t="n">
-        <v/>
-      </c>
       <c r="Q74" t="inlineStr">
         <is>
           <t>D0=610.26; 最新=2026-06-02; 相对D0=-2.07%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -5634,24 +4596,12 @@
       <c r="J75" s="4" t="n">
         <v>30.57</v>
       </c>
-      <c r="K75" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L75" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M75" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N75" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O75" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P75" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K75" s="4" t="n"/>
+      <c r="L75" s="4" t="n"/>
+      <c r="M75" s="4" t="n"/>
+      <c r="N75" s="4" t="n"/>
+      <c r="O75" s="4" t="n"/>
+      <c r="P75" s="4" t="n"/>
       <c r="Q75" s="4" t="inlineStr">
         <is>
           <t>D0=26.73; 最新=2026-06-02; 相对D0=14.37%</t>
@@ -5703,24 +4653,6 @@
       <c r="J76" t="n">
         <v>258.69</v>
       </c>
-      <c r="K76" t="n">
-        <v/>
-      </c>
-      <c r="L76" t="n">
-        <v/>
-      </c>
-      <c r="M76" t="n">
-        <v/>
-      </c>
-      <c r="N76" t="n">
-        <v/>
-      </c>
-      <c r="O76" t="n">
-        <v/>
-      </c>
-      <c r="P76" t="n">
-        <v/>
-      </c>
       <c r="Q76" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-06-02; 相对D0=11.50%</t>
@@ -5772,24 +4704,6 @@
       <c r="J77" t="n">
         <v>152.22</v>
       </c>
-      <c r="K77" t="n">
-        <v/>
-      </c>
-      <c r="L77" t="n">
-        <v/>
-      </c>
-      <c r="M77" t="n">
-        <v/>
-      </c>
-      <c r="N77" t="n">
-        <v/>
-      </c>
-      <c r="O77" t="n">
-        <v/>
-      </c>
-      <c r="P77" t="n">
-        <v/>
-      </c>
       <c r="Q77" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-06-02; 相对D0=16.64%</t>
@@ -5841,24 +4755,12 @@
       <c r="J78" s="4" t="n">
         <v>59.09</v>
       </c>
-      <c r="K78" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L78" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M78" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N78" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O78" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P78" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K78" s="4" t="n"/>
+      <c r="L78" s="4" t="n"/>
+      <c r="M78" s="4" t="n"/>
+      <c r="N78" s="4" t="n"/>
+      <c r="O78" s="4" t="n"/>
+      <c r="P78" s="4" t="n"/>
       <c r="Q78" s="4" t="inlineStr">
         <is>
           <t>D0=58.81; 最新=2026-06-02; 相对D0=0.48%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -5910,24 +4812,12 @@
       <c r="J79" s="4" t="n">
         <v>109.1</v>
       </c>
-      <c r="K79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P79" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K79" s="4" t="n"/>
+      <c r="L79" s="4" t="n"/>
+      <c r="M79" s="4" t="n"/>
+      <c r="N79" s="4" t="n"/>
+      <c r="O79" s="4" t="n"/>
+      <c r="P79" s="4" t="n"/>
       <c r="Q79" s="4" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-06-02; 相对D0=27.72%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -5979,24 +4869,6 @@
       <c r="J80" t="n">
         <v>423.74</v>
       </c>
-      <c r="K80" t="n">
-        <v/>
-      </c>
-      <c r="L80" t="n">
-        <v/>
-      </c>
-      <c r="M80" t="n">
-        <v/>
-      </c>
-      <c r="N80" t="n">
-        <v/>
-      </c>
-      <c r="O80" t="n">
-        <v/>
-      </c>
-      <c r="P80" t="n">
-        <v/>
-      </c>
       <c r="Q80" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-06-02; 相对D0=-0.53%</t>
@@ -6048,24 +4920,6 @@
       <c r="J81" t="n">
         <v>378.11</v>
       </c>
-      <c r="K81" t="n">
-        <v/>
-      </c>
-      <c r="L81" t="n">
-        <v/>
-      </c>
-      <c r="M81" t="n">
-        <v/>
-      </c>
-      <c r="N81" t="n">
-        <v/>
-      </c>
-      <c r="O81" t="n">
-        <v/>
-      </c>
-      <c r="P81" t="n">
-        <v/>
-      </c>
       <c r="Q81" t="inlineStr">
         <is>
           <t>D0=388.47; 最新=2026-06-02; 相对D0=-2.67%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -6117,24 +4971,12 @@
       <c r="J82" s="4" t="n">
         <v>74.73999999999999</v>
       </c>
-      <c r="K82" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L82" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M82" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N82" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O82" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P82" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K82" s="4" t="n"/>
+      <c r="L82" s="4" t="n"/>
+      <c r="M82" s="4" t="n"/>
+      <c r="N82" s="4" t="n"/>
+      <c r="O82" s="4" t="n"/>
+      <c r="P82" s="4" t="n"/>
       <c r="Q82" s="4" t="inlineStr">
         <is>
           <t>D0=73.46; 最新=2026-06-02; 相对D0=1.74%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -6186,24 +5028,6 @@
       <c r="J83" t="n">
         <v>481.57</v>
       </c>
-      <c r="K83" t="n">
-        <v/>
-      </c>
-      <c r="L83" t="n">
-        <v/>
-      </c>
-      <c r="M83" t="n">
-        <v/>
-      </c>
-      <c r="N83" t="n">
-        <v/>
-      </c>
-      <c r="O83" t="n">
-        <v/>
-      </c>
-      <c r="P83" t="n">
-        <v/>
-      </c>
       <c r="Q83" t="inlineStr">
         <is>
           <t>D0=422.01; 最新=2026-06-02; 相对D0=14.11%</t>
@@ -6255,24 +5079,6 @@
       <c r="J84" t="n">
         <v>93.14</v>
       </c>
-      <c r="K84" t="n">
-        <v/>
-      </c>
-      <c r="L84" t="n">
-        <v/>
-      </c>
-      <c r="M84" t="n">
-        <v/>
-      </c>
-      <c r="N84" t="n">
-        <v/>
-      </c>
-      <c r="O84" t="n">
-        <v/>
-      </c>
-      <c r="P84" t="n">
-        <v/>
-      </c>
       <c r="Q84" t="inlineStr">
         <is>
           <t>D0=86.49; 最新=2026-06-02; 相对D0=7.69%</t>
@@ -6324,24 +5130,12 @@
       <c r="J85" s="4" t="n">
         <v>187.254</v>
       </c>
-      <c r="K85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P85" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K85" s="4" t="n"/>
+      <c r="L85" s="4" t="n"/>
+      <c r="M85" s="4" t="n"/>
+      <c r="N85" s="4" t="n"/>
+      <c r="O85" s="4" t="n"/>
+      <c r="P85" s="4" t="n"/>
       <c r="Q85" s="4" t="inlineStr">
         <is>
           <t>D0=204.38; 最新=2026-06-02; 相对D0=-8.38%</t>
@@ -6393,24 +5187,12 @@
       <c r="J86" s="4" t="n">
         <v>187.24</v>
       </c>
-      <c r="K86" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L86" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M86" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N86" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O86" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P86" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K86" s="4" t="n"/>
+      <c r="L86" s="4" t="n"/>
+      <c r="M86" s="4" t="n"/>
+      <c r="N86" s="4" t="n"/>
+      <c r="O86" s="4" t="n"/>
+      <c r="P86" s="4" t="n"/>
       <c r="Q86" s="4" t="inlineStr">
         <is>
           <t>D0=174.73; 最新=2026-06-02; 相对D0=7.16%</t>
@@ -6462,24 +5244,12 @@
       <c r="J87" s="4" t="n">
         <v>120.51</v>
       </c>
-      <c r="K87" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L87" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M87" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N87" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O87" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P87" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K87" s="4" t="n"/>
+      <c r="L87" s="4" t="n"/>
+      <c r="M87" s="4" t="n"/>
+      <c r="N87" s="4" t="n"/>
+      <c r="O87" s="4" t="n"/>
+      <c r="P87" s="4" t="n"/>
       <c r="Q87" s="4" t="inlineStr">
         <is>
           <t>D0=108.17; 最新=2026-06-02; 相对D0=11.41%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -6531,24 +5301,6 @@
       <c r="J88" t="n">
         <v>119.27</v>
       </c>
-      <c r="K88" t="n">
-        <v/>
-      </c>
-      <c r="L88" t="n">
-        <v/>
-      </c>
-      <c r="M88" t="n">
-        <v/>
-      </c>
-      <c r="N88" t="n">
-        <v/>
-      </c>
-      <c r="O88" t="n">
-        <v/>
-      </c>
-      <c r="P88" t="n">
-        <v/>
-      </c>
       <c r="Q88" t="inlineStr">
         <is>
           <t>D0=105.89; 最新=2026-06-02; 相对D0=12.64%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -6600,24 +5352,12 @@
       <c r="J89" s="4" t="n">
         <v>48.67</v>
       </c>
-      <c r="K89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P89" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K89" s="4" t="n"/>
+      <c r="L89" s="4" t="n"/>
+      <c r="M89" s="4" t="n"/>
+      <c r="N89" s="4" t="n"/>
+      <c r="O89" s="4" t="n"/>
+      <c r="P89" s="4" t="n"/>
       <c r="Q89" s="4" t="inlineStr">
         <is>
           <t>D0=49.46; 最新=2026-06-02; 相对D0=-1.60%</t>
@@ -6669,24 +5409,12 @@
       <c r="J90" s="4" t="n">
         <v>417.88</v>
       </c>
-      <c r="K90" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L90" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M90" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N90" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O90" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P90" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K90" s="4" t="n"/>
+      <c r="L90" s="4" t="n"/>
+      <c r="M90" s="4" t="n"/>
+      <c r="N90" s="4" t="n"/>
+      <c r="O90" s="4" t="n"/>
+      <c r="P90" s="4" t="n"/>
       <c r="Q90" s="4" t="inlineStr">
         <is>
           <t>D0=403.13; 最新=2026-06-02; 相对D0=3.66%</t>
@@ -6738,24 +5466,12 @@
       <c r="J91" s="4" t="n">
         <v>969.62</v>
       </c>
-      <c r="K91" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L91" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M91" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N91" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O91" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P91" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K91" s="4" t="n"/>
+      <c r="L91" s="4" t="n"/>
+      <c r="M91" s="4" t="n"/>
+      <c r="N91" s="4" t="n"/>
+      <c r="O91" s="4" t="n"/>
+      <c r="P91" s="4" t="n"/>
       <c r="Q91" s="4" t="inlineStr">
         <is>
           <t>D0=1070.47; 最新=2026-06-02; 相对D0=-9.42%</t>
@@ -6807,24 +5523,6 @@
       <c r="J92" t="n">
         <v>361.84</v>
       </c>
-      <c r="K92" t="n">
-        <v/>
-      </c>
-      <c r="L92" t="n">
-        <v/>
-      </c>
-      <c r="M92" t="n">
-        <v/>
-      </c>
-      <c r="N92" t="n">
-        <v/>
-      </c>
-      <c r="O92" t="n">
-        <v/>
-      </c>
-      <c r="P92" t="n">
-        <v/>
-      </c>
       <c r="Q92" t="inlineStr">
         <is>
           <t>D0=388.88; 最新=2026-06-02; 相对D0=-6.95%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -6876,24 +5574,12 @@
       <c r="J93" s="4" t="n">
         <v>199.12</v>
       </c>
-      <c r="K93" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L93" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M93" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N93" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O93" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P93" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K93" s="4" t="n"/>
+      <c r="L93" s="4" t="n"/>
+      <c r="M93" s="4" t="n"/>
+      <c r="N93" s="4" t="n"/>
+      <c r="O93" s="4" t="n"/>
+      <c r="P93" s="4" t="n"/>
       <c r="Q93" s="4" t="inlineStr">
         <is>
           <t>D0=183.36; 最新=2026-06-02; 相对D0=8.60%</t>
@@ -6945,24 +5631,6 @@
       <c r="J94" t="n">
         <v>69.2</v>
       </c>
-      <c r="K94" t="n">
-        <v/>
-      </c>
-      <c r="L94" t="n">
-        <v/>
-      </c>
-      <c r="M94" t="n">
-        <v/>
-      </c>
-      <c r="N94" t="n">
-        <v/>
-      </c>
-      <c r="O94" t="n">
-        <v/>
-      </c>
-      <c r="P94" t="n">
-        <v/>
-      </c>
       <c r="Q94" t="inlineStr">
         <is>
           <t>D0=69.63; 最新=2026-06-02; 相对D0=-0.62%</t>
@@ -7014,24 +5682,6 @@
       <c r="J95" t="n">
         <v>597.63</v>
       </c>
-      <c r="K95" t="n">
-        <v/>
-      </c>
-      <c r="L95" t="n">
-        <v/>
-      </c>
-      <c r="M95" t="n">
-        <v/>
-      </c>
-      <c r="N95" t="n">
-        <v/>
-      </c>
-      <c r="O95" t="n">
-        <v/>
-      </c>
-      <c r="P95" t="n">
-        <v/>
-      </c>
       <c r="Q95" t="inlineStr">
         <is>
           <t>D0=612.34; 最新=2026-06-02; 相对D0=-2.40%</t>
@@ -7083,24 +5733,6 @@
       <c r="J96" t="n">
         <v>23.305</v>
       </c>
-      <c r="K96" t="n">
-        <v/>
-      </c>
-      <c r="L96" t="n">
-        <v/>
-      </c>
-      <c r="M96" t="n">
-        <v/>
-      </c>
-      <c r="N96" t="n">
-        <v/>
-      </c>
-      <c r="O96" t="n">
-        <v/>
-      </c>
-      <c r="P96" t="n">
-        <v/>
-      </c>
       <c r="Q96" t="inlineStr">
         <is>
           <t>D0=22.62; 最新=2026-06-02; 相对D0=3.03%</t>
@@ -7152,24 +5784,12 @@
       <c r="J97" s="4" t="n">
         <v>278.01</v>
       </c>
-      <c r="K97" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L97" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M97" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N97" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O97" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P97" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K97" s="4" t="n"/>
+      <c r="L97" s="4" t="n"/>
+      <c r="M97" s="4" t="n"/>
+      <c r="N97" s="4" t="n"/>
+      <c r="O97" s="4" t="n"/>
+      <c r="P97" s="4" t="n"/>
       <c r="Q97" s="4" t="inlineStr">
         <is>
           <t>D0=274.17; 最新=2026-06-02; 相对D0=1.40%</t>
@@ -7221,24 +5841,6 @@
       <c r="J98" t="n">
         <v>56.89</v>
       </c>
-      <c r="K98" t="n">
-        <v/>
-      </c>
-      <c r="L98" t="n">
-        <v/>
-      </c>
-      <c r="M98" t="n">
-        <v/>
-      </c>
-      <c r="N98" t="n">
-        <v/>
-      </c>
-      <c r="O98" t="n">
-        <v/>
-      </c>
-      <c r="P98" t="n">
-        <v/>
-      </c>
       <c r="Q98" t="inlineStr">
         <is>
           <t>D0=56.31; 最新=2026-06-02; 相对D0=1.03%</t>
@@ -7290,24 +5892,6 @@
       <c r="J99" t="n">
         <v>111.67</v>
       </c>
-      <c r="K99" t="n">
-        <v/>
-      </c>
-      <c r="L99" t="n">
-        <v/>
-      </c>
-      <c r="M99" t="n">
-        <v/>
-      </c>
-      <c r="N99" t="n">
-        <v/>
-      </c>
-      <c r="O99" t="n">
-        <v/>
-      </c>
-      <c r="P99" t="n">
-        <v/>
-      </c>
       <c r="Q99" t="inlineStr">
         <is>
           <t>D0=106.94; 最新=2026-06-02; 相对D0=4.42%</t>
@@ -7359,24 +5943,12 @@
       <c r="J100" s="4" t="n">
         <v>13.96</v>
       </c>
-      <c r="K100" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L100" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M100" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N100" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O100" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P100" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K100" s="4" t="n"/>
+      <c r="L100" s="4" t="n"/>
+      <c r="M100" s="4" t="n"/>
+      <c r="N100" s="4" t="n"/>
+      <c r="O100" s="4" t="n"/>
+      <c r="P100" s="4" t="n"/>
       <c r="Q100" s="4" t="inlineStr">
         <is>
           <t>D0=12.22; 最新=2026-06-02; 相对D0=14.24%</t>
@@ -7428,24 +6000,6 @@
       <c r="J101" t="n">
         <v>17.73</v>
       </c>
-      <c r="K101" t="n">
-        <v/>
-      </c>
-      <c r="L101" t="n">
-        <v/>
-      </c>
-      <c r="M101" t="n">
-        <v/>
-      </c>
-      <c r="N101" t="n">
-        <v/>
-      </c>
-      <c r="O101" t="n">
-        <v/>
-      </c>
-      <c r="P101" t="n">
-        <v/>
-      </c>
       <c r="Q101" t="inlineStr">
         <is>
           <t>D0=15.98; 最新=2026-06-02; 相对D0=10.95%</t>
@@ -7497,24 +6051,6 @@
       <c r="J102" t="n">
         <v>87.39</v>
       </c>
-      <c r="K102" t="n">
-        <v/>
-      </c>
-      <c r="L102" t="n">
-        <v/>
-      </c>
-      <c r="M102" t="n">
-        <v/>
-      </c>
-      <c r="N102" t="n">
-        <v/>
-      </c>
-      <c r="O102" t="n">
-        <v/>
-      </c>
-      <c r="P102" t="n">
-        <v/>
-      </c>
       <c r="Q102" t="inlineStr">
         <is>
           <t>D0=84.64; 最新=2026-06-02; 相对D0=3.25%</t>
@@ -7566,24 +6102,12 @@
       <c r="J103" s="4" t="n">
         <v>15.445</v>
       </c>
-      <c r="K103" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L103" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M103" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N103" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O103" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P103" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K103" s="4" t="n"/>
+      <c r="L103" s="4" t="n"/>
+      <c r="M103" s="4" t="n"/>
+      <c r="N103" s="4" t="n"/>
+      <c r="O103" s="4" t="n"/>
+      <c r="P103" s="4" t="n"/>
       <c r="Q103" s="4" t="inlineStr">
         <is>
           <t>D0=13.51; 最新=2026-06-02; 相对D0=14.32%</t>
@@ -7635,24 +6159,6 @@
       <c r="J104" t="n">
         <v>51.51</v>
       </c>
-      <c r="K104" t="n">
-        <v/>
-      </c>
-      <c r="L104" t="n">
-        <v/>
-      </c>
-      <c r="M104" t="n">
-        <v/>
-      </c>
-      <c r="N104" t="n">
-        <v/>
-      </c>
-      <c r="O104" t="n">
-        <v/>
-      </c>
-      <c r="P104" t="n">
-        <v/>
-      </c>
       <c r="Q104" t="inlineStr">
         <is>
           <t>D0=50.99; 最新=2026-06-02; 相对D0=1.02%</t>
@@ -7704,24 +6210,6 @@
       <c r="J105" t="n">
         <v>202.37</v>
       </c>
-      <c r="K105" t="n">
-        <v/>
-      </c>
-      <c r="L105" t="n">
-        <v/>
-      </c>
-      <c r="M105" t="n">
-        <v/>
-      </c>
-      <c r="N105" t="n">
-        <v/>
-      </c>
-      <c r="O105" t="n">
-        <v/>
-      </c>
-      <c r="P105" t="n">
-        <v/>
-      </c>
       <c r="Q105" t="inlineStr">
         <is>
           <t>D0=179.83; 最新=2026-06-02; 相对D0=12.53%</t>
@@ -7773,24 +6261,6 @@
       <c r="J106" t="n">
         <v>256.52</v>
       </c>
-      <c r="K106" t="n">
-        <v/>
-      </c>
-      <c r="L106" t="n">
-        <v/>
-      </c>
-      <c r="M106" t="n">
-        <v/>
-      </c>
-      <c r="N106" t="n">
-        <v/>
-      </c>
-      <c r="O106" t="n">
-        <v/>
-      </c>
-      <c r="P106" t="n">
-        <v/>
-      </c>
       <c r="Q106" t="inlineStr">
         <is>
           <t>D0=271.85; 最新=2026-06-02; 相对D0=-5.64%</t>
@@ -7811,7 +6281,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -7838,24 +6307,6 @@
       <c r="J107" t="n">
         <v>89.92</v>
       </c>
-      <c r="K107" t="n">
-        <v/>
-      </c>
-      <c r="L107" t="n">
-        <v/>
-      </c>
-      <c r="M107" t="n">
-        <v/>
-      </c>
-      <c r="N107" t="n">
-        <v/>
-      </c>
-      <c r="O107" t="n">
-        <v/>
-      </c>
-      <c r="P107" t="n">
-        <v/>
-      </c>
       <c r="Q107" t="inlineStr">
         <is>
           <t>D0=90.87; 最新=2026-06-02; 相对D0=-1.05%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -7907,24 +6358,6 @@
       <c r="J108" t="n">
         <v>16.755</v>
       </c>
-      <c r="K108" t="n">
-        <v/>
-      </c>
-      <c r="L108" t="n">
-        <v/>
-      </c>
-      <c r="M108" t="n">
-        <v/>
-      </c>
-      <c r="N108" t="n">
-        <v/>
-      </c>
-      <c r="O108" t="n">
-        <v/>
-      </c>
-      <c r="P108" t="n">
-        <v/>
-      </c>
       <c r="Q108" t="inlineStr">
         <is>
           <t>D0=16.46; 最新=2026-06-02; 相对D0=1.79%</t>
@@ -7976,24 +6409,6 @@
       <c r="J109" t="n">
         <v>27.51</v>
       </c>
-      <c r="K109" t="n">
-        <v/>
-      </c>
-      <c r="L109" t="n">
-        <v/>
-      </c>
-      <c r="M109" t="n">
-        <v/>
-      </c>
-      <c r="N109" t="n">
-        <v/>
-      </c>
-      <c r="O109" t="n">
-        <v/>
-      </c>
-      <c r="P109" t="n">
-        <v/>
-      </c>
       <c r="Q109" t="inlineStr">
         <is>
           <t>D0=25.20; 最新=2026-06-02; 相对D0=9.17%</t>
@@ -8045,24 +6460,6 @@
       <c r="J110" t="n">
         <v>88.16</v>
       </c>
-      <c r="K110" t="n">
-        <v/>
-      </c>
-      <c r="L110" t="n">
-        <v/>
-      </c>
-      <c r="M110" t="n">
-        <v/>
-      </c>
-      <c r="N110" t="n">
-        <v/>
-      </c>
-      <c r="O110" t="n">
-        <v/>
-      </c>
-      <c r="P110" t="n">
-        <v/>
-      </c>
       <c r="Q110" t="inlineStr">
         <is>
           <t>D0=76.23; 最新=2026-06-02; 相对D0=15.65%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -8114,24 +6511,6 @@
       <c r="J111" t="n">
         <v>49.93</v>
       </c>
-      <c r="K111" t="n">
-        <v/>
-      </c>
-      <c r="L111" t="n">
-        <v/>
-      </c>
-      <c r="M111" t="n">
-        <v/>
-      </c>
-      <c r="N111" t="n">
-        <v/>
-      </c>
-      <c r="O111" t="n">
-        <v/>
-      </c>
-      <c r="P111" t="n">
-        <v/>
-      </c>
       <c r="Q111" t="inlineStr">
         <is>
           <t>D0=50.44; 最新=2026-06-02; 相对D0=-1.01%</t>
@@ -8183,24 +6562,12 @@
       <c r="J112" s="4" t="n">
         <v>127.64</v>
       </c>
-      <c r="K112" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L112" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M112" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N112" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O112" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P112" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K112" s="4" t="n"/>
+      <c r="L112" s="4" t="n"/>
+      <c r="M112" s="4" t="n"/>
+      <c r="N112" s="4" t="n"/>
+      <c r="O112" s="4" t="n"/>
+      <c r="P112" s="4" t="n"/>
       <c r="Q112" s="4" t="inlineStr">
         <is>
           <t>D0=102.12; 最新=2026-06-02; 相对D0=24.99%</t>
@@ -8252,24 +6619,12 @@
       <c r="J113" s="4" t="n">
         <v>278.01</v>
       </c>
-      <c r="K113" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L113" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M113" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N113" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O113" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P113" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K113" s="4" t="n"/>
+      <c r="L113" s="4" t="n"/>
+      <c r="M113" s="4" t="n"/>
+      <c r="N113" s="4" t="n"/>
+      <c r="O113" s="4" t="n"/>
+      <c r="P113" s="4" t="n"/>
       <c r="Q113" s="4" t="inlineStr">
         <is>
           <t>D0=266.89; 最新=2026-06-02; 相对D0=4.17%</t>
@@ -8321,24 +6676,6 @@
       <c r="J114" t="n">
         <v>244.542</v>
       </c>
-      <c r="K114" t="n">
-        <v/>
-      </c>
-      <c r="L114" t="n">
-        <v/>
-      </c>
-      <c r="M114" t="n">
-        <v/>
-      </c>
-      <c r="N114" t="n">
-        <v/>
-      </c>
-      <c r="O114" t="n">
-        <v/>
-      </c>
-      <c r="P114" t="n">
-        <v/>
-      </c>
       <c r="Q114" t="inlineStr">
         <is>
           <t>D0=190.96; 最新=2026-06-02; 相对D0=28.06%</t>
@@ -8390,24 +6727,12 @@
       <c r="J115" s="4" t="n">
         <v>109.1</v>
       </c>
-      <c r="K115" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L115" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M115" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N115" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O115" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P115" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K115" s="4" t="n"/>
+      <c r="L115" s="4" t="n"/>
+      <c r="M115" s="4" t="n"/>
+      <c r="N115" s="4" t="n"/>
+      <c r="O115" s="4" t="n"/>
+      <c r="P115" s="4" t="n"/>
       <c r="Q115" s="4" t="inlineStr">
         <is>
           <t>D0=89.07; 最新=2026-06-02; 相对D0=22.49%</t>
@@ -8459,24 +6784,6 @@
       <c r="J116" t="n">
         <v>378.11</v>
       </c>
-      <c r="K116" t="n">
-        <v/>
-      </c>
-      <c r="L116" t="n">
-        <v/>
-      </c>
-      <c r="M116" t="n">
-        <v/>
-      </c>
-      <c r="N116" t="n">
-        <v/>
-      </c>
-      <c r="O116" t="n">
-        <v/>
-      </c>
-      <c r="P116" t="n">
-        <v/>
-      </c>
       <c r="Q116" t="inlineStr">
         <is>
           <t>D0=384.01; 最新=2026-06-02; 相对D0=-1.54%</t>
@@ -8497,7 +6804,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -8524,24 +6830,6 @@
       <c r="J117" t="n">
         <v>89.92</v>
       </c>
-      <c r="K117" t="n">
-        <v/>
-      </c>
-      <c r="L117" t="n">
-        <v/>
-      </c>
-      <c r="M117" t="n">
-        <v/>
-      </c>
-      <c r="N117" t="n">
-        <v/>
-      </c>
-      <c r="O117" t="n">
-        <v/>
-      </c>
-      <c r="P117" t="n">
-        <v/>
-      </c>
       <c r="Q117" t="inlineStr">
         <is>
           <t>D0=91.09; 最新=2026-06-02; 相对D0=-1.28%</t>
@@ -8593,24 +6881,12 @@
       <c r="J118" s="4" t="n">
         <v>120.51</v>
       </c>
-      <c r="K118" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L118" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M118" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N118" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O118" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P118" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K118" s="4" t="n"/>
+      <c r="L118" s="4" t="n"/>
+      <c r="M118" s="4" t="n"/>
+      <c r="N118" s="4" t="n"/>
+      <c r="O118" s="4" t="n"/>
+      <c r="P118" s="4" t="n"/>
       <c r="Q118" s="4" t="inlineStr">
         <is>
           <t>D0=110.63; 最新=2026-06-02; 相对D0=8.93%</t>
@@ -8662,24 +6938,6 @@
       <c r="J119" t="n">
         <v>94.34</v>
       </c>
-      <c r="K119" t="n">
-        <v/>
-      </c>
-      <c r="L119" t="n">
-        <v/>
-      </c>
-      <c r="M119" t="n">
-        <v/>
-      </c>
-      <c r="N119" t="n">
-        <v/>
-      </c>
-      <c r="O119" t="n">
-        <v/>
-      </c>
-      <c r="P119" t="n">
-        <v/>
-      </c>
       <c r="Q119" t="inlineStr">
         <is>
           <t>D0=83.68; 最新=2026-06-02; 相对D0=12.74%</t>
@@ -8731,24 +6989,12 @@
       <c r="J120" s="4" t="n">
         <v>200.83</v>
       </c>
-      <c r="K120" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L120" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M120" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N120" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O120" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P120" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K120" s="4" t="n"/>
+      <c r="L120" s="4" t="n"/>
+      <c r="M120" s="4" t="n"/>
+      <c r="N120" s="4" t="n"/>
+      <c r="O120" s="4" t="n"/>
+      <c r="P120" s="4" t="n"/>
       <c r="Q120" s="4" t="inlineStr">
         <is>
           <t>D0=176.17; 最新=2026-06-02; 相对D0=14.00%</t>
@@ -8800,24 +7046,6 @@
       <c r="J121" t="n">
         <v>768.35</v>
       </c>
-      <c r="K121" t="n">
-        <v/>
-      </c>
-      <c r="L121" t="n">
-        <v/>
-      </c>
-      <c r="M121" t="n">
-        <v/>
-      </c>
-      <c r="N121" t="n">
-        <v/>
-      </c>
-      <c r="O121" t="n">
-        <v/>
-      </c>
-      <c r="P121" t="n">
-        <v/>
-      </c>
       <c r="Q121" t="inlineStr">
         <is>
           <t>D0=671.00; 最新=2026-06-02; 相对D0=14.51%</t>
@@ -8869,24 +7097,6 @@
       <c r="J122" t="n">
         <v>119.27</v>
       </c>
-      <c r="K122" t="n">
-        <v/>
-      </c>
-      <c r="L122" t="n">
-        <v/>
-      </c>
-      <c r="M122" t="n">
-        <v/>
-      </c>
-      <c r="N122" t="n">
-        <v/>
-      </c>
-      <c r="O122" t="n">
-        <v/>
-      </c>
-      <c r="P122" t="n">
-        <v/>
-      </c>
       <c r="Q122" t="inlineStr">
         <is>
           <t>D0=106.86; 最新=2026-06-02; 相对D0=11.61%</t>
@@ -8907,7 +7117,6 @@
           <t>EQIX</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -8934,24 +7143,6 @@
       <c r="J123" t="n">
         <v>1071.67</v>
       </c>
-      <c r="K123" t="n">
-        <v/>
-      </c>
-      <c r="L123" t="n">
-        <v/>
-      </c>
-      <c r="M123" t="n">
-        <v/>
-      </c>
-      <c r="N123" t="n">
-        <v/>
-      </c>
-      <c r="O123" t="n">
-        <v/>
-      </c>
-      <c r="P123" t="n">
-        <v/>
-      </c>
       <c r="Q123" t="inlineStr">
         <is>
           <t>D0=1069.44; 最新=2026-06-02; 相对D0=0.21%</t>
@@ -9003,24 +7194,6 @@
       <c r="J124" t="n">
         <v>148.87</v>
       </c>
-      <c r="K124" t="n">
-        <v/>
-      </c>
-      <c r="L124" t="n">
-        <v/>
-      </c>
-      <c r="M124" t="n">
-        <v/>
-      </c>
-      <c r="N124" t="n">
-        <v/>
-      </c>
-      <c r="O124" t="n">
-        <v/>
-      </c>
-      <c r="P124" t="n">
-        <v/>
-      </c>
       <c r="Q124" t="inlineStr">
         <is>
           <t>D0=129.70; 最新=2026-06-02; 相对D0=14.78%</t>
@@ -9072,24 +7245,6 @@
       <c r="J125" t="n">
         <v>361.84</v>
       </c>
-      <c r="K125" t="n">
-        <v/>
-      </c>
-      <c r="L125" t="n">
-        <v/>
-      </c>
-      <c r="M125" t="n">
-        <v/>
-      </c>
-      <c r="N125" t="n">
-        <v/>
-      </c>
-      <c r="O125" t="n">
-        <v/>
-      </c>
-      <c r="P125" t="n">
-        <v/>
-      </c>
       <c r="Q125" t="inlineStr">
         <is>
           <t>D0=390.13; 最新=2026-06-02; 相对D0=-7.25%</t>
@@ -9141,24 +7296,6 @@
       <c r="J126" t="n">
         <v>88.16</v>
       </c>
-      <c r="K126" t="n">
-        <v/>
-      </c>
-      <c r="L126" t="n">
-        <v/>
-      </c>
-      <c r="M126" t="n">
-        <v/>
-      </c>
-      <c r="N126" t="n">
-        <v/>
-      </c>
-      <c r="O126" t="n">
-        <v/>
-      </c>
-      <c r="P126" t="n">
-        <v/>
-      </c>
       <c r="Q126" t="inlineStr">
         <is>
           <t>D0=84.84; 最新=2026-06-02; 相对D0=3.91%</t>
@@ -9210,24 +7347,12 @@
       <c r="J127" s="4" t="n">
         <v>104.78</v>
       </c>
-      <c r="K127" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L127" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M127" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N127" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O127" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P127" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K127" s="4" t="n"/>
+      <c r="L127" s="4" t="n"/>
+      <c r="M127" s="4" t="n"/>
+      <c r="N127" s="4" t="n"/>
+      <c r="O127" s="4" t="n"/>
+      <c r="P127" s="4" t="n"/>
       <c r="Q127" s="4" t="inlineStr">
         <is>
           <t>D0=95.68; 最新=2026-06-02; 相对D0=9.51%</t>
@@ -9279,24 +7404,12 @@
       <c r="J128" s="4" t="n">
         <v>199.12</v>
       </c>
-      <c r="K128" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L128" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M128" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N128" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O128" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P128" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K128" s="4" t="n"/>
+      <c r="L128" s="4" t="n"/>
+      <c r="M128" s="4" t="n"/>
+      <c r="N128" s="4" t="n"/>
+      <c r="O128" s="4" t="n"/>
+      <c r="P128" s="4" t="n"/>
       <c r="Q128" s="4" t="inlineStr">
         <is>
           <t>D0=185.46; 最新=2026-06-02; 相对D0=7.37%</t>
@@ -9348,24 +7461,12 @@
       <c r="J129" s="4" t="n">
         <v>398.46</v>
       </c>
-      <c r="K129" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L129" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M129" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N129" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O129" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P129" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K129" s="4" t="n"/>
+      <c r="L129" s="4" t="n"/>
+      <c r="M129" s="4" t="n"/>
+      <c r="N129" s="4" t="n"/>
+      <c r="O129" s="4" t="n"/>
+      <c r="P129" s="4" t="n"/>
       <c r="Q129" s="4" t="inlineStr">
         <is>
           <t>D0=325.68; 最新=2026-06-02; 相对D0=22.35%</t>
@@ -9417,24 +7518,6 @@
       <c r="J130" t="n">
         <v>441.31</v>
       </c>
-      <c r="K130" t="n">
-        <v/>
-      </c>
-      <c r="L130" t="n">
-        <v/>
-      </c>
-      <c r="M130" t="n">
-        <v/>
-      </c>
-      <c r="N130" t="n">
-        <v/>
-      </c>
-      <c r="O130" t="n">
-        <v/>
-      </c>
-      <c r="P130" t="n">
-        <v/>
-      </c>
       <c r="Q130" t="inlineStr">
         <is>
           <t>D0=426.99; 最新=2026-06-02; 相对D0=3.35%</t>
@@ -9486,24 +7569,6 @@
       <c r="J131" t="n">
         <v>260.58</v>
       </c>
-      <c r="K131" t="n">
-        <v/>
-      </c>
-      <c r="L131" t="n">
-        <v/>
-      </c>
-      <c r="M131" t="n">
-        <v/>
-      </c>
-      <c r="N131" t="n">
-        <v/>
-      </c>
-      <c r="O131" t="n">
-        <v/>
-      </c>
-      <c r="P131" t="n">
-        <v/>
-      </c>
       <c r="Q131" t="inlineStr">
         <is>
           <t>D0=226.34; 最新=2026-06-02; 相对D0=15.13%</t>
@@ -9555,24 +7620,12 @@
       <c r="J132" s="4" t="n">
         <v>137.91</v>
       </c>
-      <c r="K132" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L132" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M132" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N132" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O132" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P132" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K132" s="4" t="n"/>
+      <c r="L132" s="4" t="n"/>
+      <c r="M132" s="4" t="n"/>
+      <c r="N132" s="4" t="n"/>
+      <c r="O132" s="4" t="n"/>
+      <c r="P132" s="4" t="n"/>
       <c r="Q132" s="4" t="inlineStr">
         <is>
           <t>D0=133.31; 最新=2026-06-02; 相对D0=3.45%</t>
@@ -9624,24 +7677,6 @@
       <c r="J133" t="n">
         <v>135.32</v>
       </c>
-      <c r="K133" t="n">
-        <v/>
-      </c>
-      <c r="L133" t="n">
-        <v/>
-      </c>
-      <c r="M133" t="n">
-        <v/>
-      </c>
-      <c r="N133" t="n">
-        <v/>
-      </c>
-      <c r="O133" t="n">
-        <v/>
-      </c>
-      <c r="P133" t="n">
-        <v/>
-      </c>
       <c r="Q133" t="inlineStr">
         <is>
           <t>D0=94.72; 最新=2026-06-02; 相对D0=42.86%</t>
@@ -9693,24 +7728,6 @@
       <c r="J134" t="n">
         <v>297.18</v>
       </c>
-      <c r="K134" t="n">
-        <v/>
-      </c>
-      <c r="L134" t="n">
-        <v/>
-      </c>
-      <c r="M134" t="n">
-        <v/>
-      </c>
-      <c r="N134" t="n">
-        <v/>
-      </c>
-      <c r="O134" t="n">
-        <v/>
-      </c>
-      <c r="P134" t="n">
-        <v/>
-      </c>
       <c r="Q134" t="inlineStr">
         <is>
           <t>D0=257.77; 最新=2026-06-02; 相对D0=15.29%</t>
@@ -9762,24 +7779,12 @@
       <c r="J135" s="4" t="n">
         <v>152.17</v>
       </c>
-      <c r="K135" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L135" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M135" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N135" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O135" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P135" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K135" s="4" t="n"/>
+      <c r="L135" s="4" t="n"/>
+      <c r="M135" s="4" t="n"/>
+      <c r="N135" s="4" t="n"/>
+      <c r="O135" s="4" t="n"/>
+      <c r="P135" s="4" t="n"/>
       <c r="Q135" s="4" t="inlineStr">
         <is>
           <t>D0=143.34; 最新=2026-06-02; 相对D0=6.16%</t>
@@ -9831,24 +7836,12 @@
       <c r="J136" s="4" t="n">
         <v>262.11</v>
       </c>
-      <c r="K136" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L136" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M136" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N136" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O136" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P136" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K136" s="4" t="n"/>
+      <c r="L136" s="4" t="n"/>
+      <c r="M136" s="4" t="n"/>
+      <c r="N136" s="4" t="n"/>
+      <c r="O136" s="4" t="n"/>
+      <c r="P136" s="4" t="n"/>
       <c r="Q136" s="4" t="inlineStr">
         <is>
           <t>D0=259.21; 最新=2026-06-02; 相对D0=1.12%</t>
@@ -9900,24 +7893,12 @@
       <c r="J137" s="4" t="n">
         <v>187.24</v>
       </c>
-      <c r="K137" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L137" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M137" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N137" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O137" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P137" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K137" s="4" t="n"/>
+      <c r="L137" s="4" t="n"/>
+      <c r="M137" s="4" t="n"/>
+      <c r="N137" s="4" t="n"/>
+      <c r="O137" s="4" t="n"/>
+      <c r="P137" s="4" t="n"/>
       <c r="Q137" s="4" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-02; 相对D0=9.08%</t>
@@ -9969,24 +7950,12 @@
       <c r="J138" s="4" t="n">
         <v>272.65</v>
       </c>
-      <c r="K138" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L138" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M138" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N138" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O138" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P138" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K138" s="4" t="n"/>
+      <c r="L138" s="4" t="n"/>
+      <c r="M138" s="4" t="n"/>
+      <c r="N138" s="4" t="n"/>
+      <c r="O138" s="4" t="n"/>
+      <c r="P138" s="4" t="n"/>
       <c r="Q138" s="4" t="inlineStr">
         <is>
           <t>D0=287.75; 最新=2026-06-02; 相对D0=-5.25%</t>
@@ -10038,24 +8007,6 @@
       <c r="J139" t="n">
         <v>173.99</v>
       </c>
-      <c r="K139" t="n">
-        <v/>
-      </c>
-      <c r="L139" t="n">
-        <v/>
-      </c>
-      <c r="M139" t="n">
-        <v/>
-      </c>
-      <c r="N139" t="n">
-        <v/>
-      </c>
-      <c r="O139" t="n">
-        <v/>
-      </c>
-      <c r="P139" t="n">
-        <v/>
-      </c>
       <c r="Q139" t="inlineStr">
         <is>
           <t>D0=189.03; 最新=2026-06-02; 相对D0=-7.96%</t>
@@ -10107,24 +8058,12 @@
       <c r="J140" s="4" t="n">
         <v>200.83</v>
       </c>
-      <c r="K140" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L140" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M140" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N140" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O140" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P140" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K140" s="4" t="n"/>
+      <c r="L140" s="4" t="n"/>
+      <c r="M140" s="4" t="n"/>
+      <c r="N140" s="4" t="n"/>
+      <c r="O140" s="4" t="n"/>
+      <c r="P140" s="4" t="n"/>
       <c r="Q140" s="4" t="inlineStr">
         <is>
           <t>D0=191.10; 最新=2026-06-02; 相对D0=5.09%</t>
@@ -10176,24 +8115,6 @@
       <c r="J141" t="n">
         <v>119.27</v>
       </c>
-      <c r="K141" t="n">
-        <v/>
-      </c>
-      <c r="L141" t="n">
-        <v/>
-      </c>
-      <c r="M141" t="n">
-        <v/>
-      </c>
-      <c r="N141" t="n">
-        <v/>
-      </c>
-      <c r="O141" t="n">
-        <v/>
-      </c>
-      <c r="P141" t="n">
-        <v/>
-      </c>
       <c r="Q141" t="inlineStr">
         <is>
           <t>D0=109.53; 最新=2026-06-02; 相对D0=8.89%</t>
@@ -10245,24 +8166,12 @@
       <c r="J142" s="4" t="n">
         <v>48.67</v>
       </c>
-      <c r="K142" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L142" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M142" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N142" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O142" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P142" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K142" s="4" t="n"/>
+      <c r="L142" s="4" t="n"/>
+      <c r="M142" s="4" t="n"/>
+      <c r="N142" s="4" t="n"/>
+      <c r="O142" s="4" t="n"/>
+      <c r="P142" s="4" t="n"/>
       <c r="Q142" s="4" t="inlineStr">
         <is>
           <t>D0=48.42; 最新=2026-06-02; 相对D0=0.52%</t>
@@ -10314,24 +8223,6 @@
       <c r="J143" t="n">
         <v>2045.2</v>
       </c>
-      <c r="K143" t="n">
-        <v/>
-      </c>
-      <c r="L143" t="n">
-        <v/>
-      </c>
-      <c r="M143" t="n">
-        <v/>
-      </c>
-      <c r="N143" t="n">
-        <v/>
-      </c>
-      <c r="O143" t="n">
-        <v/>
-      </c>
-      <c r="P143" t="n">
-        <v/>
-      </c>
       <c r="Q143" t="inlineStr">
         <is>
           <t>D0=1921.71; 最新=2026-06-02; 相对D0=6.43%</t>
@@ -10383,24 +8274,12 @@
       <c r="J144" s="4" t="n">
         <v>398.46</v>
       </c>
-      <c r="K144" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L144" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M144" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N144" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O144" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P144" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K144" s="4" t="n"/>
+      <c r="L144" s="4" t="n"/>
+      <c r="M144" s="4" t="n"/>
+      <c r="N144" s="4" t="n"/>
+      <c r="O144" s="4" t="n"/>
+      <c r="P144" s="4" t="n"/>
       <c r="Q144" s="4" t="inlineStr">
         <is>
           <t>D0=335.55; 最新=2026-06-02; 相对D0=18.75%</t>
@@ -10452,24 +8331,6 @@
       <c r="J145" t="n">
         <v>222.82</v>
       </c>
-      <c r="K145" t="n">
-        <v/>
-      </c>
-      <c r="L145" t="n">
-        <v/>
-      </c>
-      <c r="M145" t="n">
-        <v/>
-      </c>
-      <c r="N145" t="n">
-        <v/>
-      </c>
-      <c r="O145" t="n">
-        <v/>
-      </c>
-      <c r="P145" t="n">
-        <v/>
-      </c>
       <c r="Q145" t="inlineStr">
         <is>
           <t>D0=211.14; 最新=2026-06-02; 相对D0=5.53%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -10521,24 +8382,12 @@
       <c r="J146" s="4" t="n">
         <v>15.445</v>
       </c>
-      <c r="K146" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L146" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M146" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N146" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O146" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P146" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K146" s="4" t="n"/>
+      <c r="L146" s="4" t="n"/>
+      <c r="M146" s="4" t="n"/>
+      <c r="N146" s="4" t="n"/>
+      <c r="O146" s="4" t="n"/>
+      <c r="P146" s="4" t="n"/>
       <c r="Q146" s="4" t="inlineStr">
         <is>
           <t>D0=13.77; 最新=2026-06-02; 相对D0=12.16%</t>
@@ -10590,24 +8439,6 @@
       <c r="J147" t="n">
         <v>51.465</v>
       </c>
-      <c r="K147" t="n">
-        <v/>
-      </c>
-      <c r="L147" t="n">
-        <v/>
-      </c>
-      <c r="M147" t="n">
-        <v/>
-      </c>
-      <c r="N147" t="n">
-        <v/>
-      </c>
-      <c r="O147" t="n">
-        <v/>
-      </c>
-      <c r="P147" t="n">
-        <v/>
-      </c>
       <c r="Q147" t="inlineStr">
         <is>
           <t>D0=51.58; 最新=2026-06-02; 相对D0=-0.22%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -10659,24 +8490,6 @@
       <c r="J148" t="n">
         <v>202.37</v>
       </c>
-      <c r="K148" t="n">
-        <v/>
-      </c>
-      <c r="L148" t="n">
-        <v/>
-      </c>
-      <c r="M148" t="n">
-        <v/>
-      </c>
-      <c r="N148" t="n">
-        <v/>
-      </c>
-      <c r="O148" t="n">
-        <v/>
-      </c>
-      <c r="P148" t="n">
-        <v/>
-      </c>
       <c r="Q148" t="inlineStr">
         <is>
           <t>D0=185.67; 最新=2026-06-02; 相对D0=8.99%</t>
@@ -10728,24 +8541,12 @@
       <c r="J149" s="4" t="n">
         <v>14.7</v>
       </c>
-      <c r="K149" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L149" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M149" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N149" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O149" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P149" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K149" s="4" t="n"/>
+      <c r="L149" s="4" t="n"/>
+      <c r="M149" s="4" t="n"/>
+      <c r="N149" s="4" t="n"/>
+      <c r="O149" s="4" t="n"/>
+      <c r="P149" s="4" t="n"/>
       <c r="Q149" s="4" t="inlineStr">
         <is>
           <t>D0=14.70; 最新=2026-06-02; 相对D0=0.00%</t>
@@ -10797,24 +8598,12 @@
       <c r="J150" s="4" t="n">
         <v>74.73999999999999</v>
       </c>
-      <c r="K150" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L150" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M150" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N150" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O150" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P150" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K150" s="4" t="n"/>
+      <c r="L150" s="4" t="n"/>
+      <c r="M150" s="4" t="n"/>
+      <c r="N150" s="4" t="n"/>
+      <c r="O150" s="4" t="n"/>
+      <c r="P150" s="4" t="n"/>
       <c r="Q150" s="4" t="inlineStr">
         <is>
           <t>D0=72.75; 最新=2026-06-02; 相对D0=2.74%</t>
@@ -10866,24 +8655,6 @@
       <c r="J151" t="n">
         <v>317.95</v>
       </c>
-      <c r="K151" t="n">
-        <v/>
-      </c>
-      <c r="L151" t="n">
-        <v/>
-      </c>
-      <c r="M151" t="n">
-        <v/>
-      </c>
-      <c r="N151" t="n">
-        <v/>
-      </c>
-      <c r="O151" t="n">
-        <v/>
-      </c>
-      <c r="P151" t="n">
-        <v/>
-      </c>
       <c r="Q151" t="inlineStr">
         <is>
           <t>D0=320.41; 最新=2026-06-02; 相对D0=-0.77%</t>
@@ -10935,24 +8706,12 @@
       <c r="J152" s="4" t="n">
         <v>138.63</v>
       </c>
-      <c r="K152" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L152" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M152" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N152" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O152" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P152" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K152" s="4" t="n"/>
+      <c r="L152" s="4" t="n"/>
+      <c r="M152" s="4" t="n"/>
+      <c r="N152" s="4" t="n"/>
+      <c r="O152" s="4" t="n"/>
+      <c r="P152" s="4" t="n"/>
       <c r="Q152" s="4" t="inlineStr">
         <is>
           <t>D0=136.62; 最新=2026-06-02; 相对D0=1.47%</t>
@@ -11004,24 +8763,6 @@
       <c r="J153" t="n">
         <v>9.404999999999999</v>
       </c>
-      <c r="K153" t="n">
-        <v/>
-      </c>
-      <c r="L153" t="n">
-        <v/>
-      </c>
-      <c r="M153" t="n">
-        <v/>
-      </c>
-      <c r="N153" t="n">
-        <v/>
-      </c>
-      <c r="O153" t="n">
-        <v/>
-      </c>
-      <c r="P153" t="n">
-        <v/>
-      </c>
       <c r="Q153" t="inlineStr">
         <is>
           <t>D0=8.97; 最新=2026-06-02; 相对D0=4.85%</t>
@@ -11073,24 +8814,6 @@
       <c r="J154" t="n">
         <v>27.9</v>
       </c>
-      <c r="K154" t="n">
-        <v/>
-      </c>
-      <c r="L154" t="n">
-        <v/>
-      </c>
-      <c r="M154" t="n">
-        <v/>
-      </c>
-      <c r="N154" t="n">
-        <v/>
-      </c>
-      <c r="O154" t="n">
-        <v/>
-      </c>
-      <c r="P154" t="n">
-        <v/>
-      </c>
       <c r="Q154" t="inlineStr">
         <is>
           <t>D0=27.15; 最新=2026-06-02; 相对D0=2.76%</t>
@@ -11142,24 +8865,6 @@
       <c r="J155" t="n">
         <v>49.93</v>
       </c>
-      <c r="K155" t="n">
-        <v/>
-      </c>
-      <c r="L155" t="n">
-        <v/>
-      </c>
-      <c r="M155" t="n">
-        <v/>
-      </c>
-      <c r="N155" t="n">
-        <v/>
-      </c>
-      <c r="O155" t="n">
-        <v/>
-      </c>
-      <c r="P155" t="n">
-        <v/>
-      </c>
       <c r="Q155" t="inlineStr">
         <is>
           <t>D0=50.55; 最新=2026-06-02; 相对D0=-1.23%</t>
@@ -11211,24 +8916,12 @@
       <c r="J156" s="4" t="n">
         <v>199.12</v>
       </c>
-      <c r="K156" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L156" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M156" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N156" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O156" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P156" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K156" s="4" t="n"/>
+      <c r="L156" s="4" t="n"/>
+      <c r="M156" s="4" t="n"/>
+      <c r="N156" s="4" t="n"/>
+      <c r="O156" s="4" t="n"/>
+      <c r="P156" s="4" t="n"/>
       <c r="Q156" s="4" t="inlineStr">
         <is>
           <t>D0=189.00; 最新=2026-06-02; 相对D0=5.35%</t>
@@ -11280,24 +8973,6 @@
       <c r="J157" t="n">
         <v>1029.15</v>
       </c>
-      <c r="K157" t="n">
-        <v/>
-      </c>
-      <c r="L157" t="n">
-        <v/>
-      </c>
-      <c r="M157" t="n">
-        <v/>
-      </c>
-      <c r="N157" t="n">
-        <v/>
-      </c>
-      <c r="O157" t="n">
-        <v/>
-      </c>
-      <c r="P157" t="n">
-        <v/>
-      </c>
       <c r="Q157" t="inlineStr">
         <is>
           <t>D0=905.00; 最新=2026-06-02; 相对D0=13.72%</t>
@@ -11349,24 +9024,6 @@
       <c r="J158" t="n">
         <v>68.5</v>
       </c>
-      <c r="K158" t="n">
-        <v/>
-      </c>
-      <c r="L158" t="n">
-        <v/>
-      </c>
-      <c r="M158" t="n">
-        <v/>
-      </c>
-      <c r="N158" t="n">
-        <v/>
-      </c>
-      <c r="O158" t="n">
-        <v/>
-      </c>
-      <c r="P158" t="n">
-        <v/>
-      </c>
       <c r="Q158" t="inlineStr">
         <is>
           <t>D0=69.57; 最新=2026-06-02; 相对D0=-1.54%</t>
@@ -11418,24 +9075,6 @@
       <c r="J159" t="n">
         <v>222.82</v>
       </c>
-      <c r="K159" t="n">
-        <v/>
-      </c>
-      <c r="L159" t="n">
-        <v/>
-      </c>
-      <c r="M159" t="n">
-        <v/>
-      </c>
-      <c r="N159" t="n">
-        <v/>
-      </c>
-      <c r="O159" t="n">
-        <v/>
-      </c>
-      <c r="P159" t="n">
-        <v/>
-      </c>
       <c r="Q159" t="inlineStr">
         <is>
           <t>D0=224.36; 最新=2026-06-02; 相对D0=-0.69%</t>
@@ -11487,24 +9126,12 @@
       <c r="J160" s="4" t="n">
         <v>73.48</v>
       </c>
-      <c r="K160" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L160" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M160" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N160" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O160" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P160" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K160" s="4" t="n"/>
+      <c r="L160" s="4" t="n"/>
+      <c r="M160" s="4" t="n"/>
+      <c r="N160" s="4" t="n"/>
+      <c r="O160" s="4" t="n"/>
+      <c r="P160" s="4" t="n"/>
       <c r="Q160" s="4" t="inlineStr">
         <is>
           <t>D0=66.89; 最新=2026-06-02; 相对D0=9.85%</t>
@@ -11556,24 +9183,12 @@
       <c r="J161" s="4" t="n">
         <v>59.09</v>
       </c>
-      <c r="K161" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L161" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M161" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N161" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O161" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P161" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K161" s="4" t="n"/>
+      <c r="L161" s="4" t="n"/>
+      <c r="M161" s="4" t="n"/>
+      <c r="N161" s="4" t="n"/>
+      <c r="O161" s="4" t="n"/>
+      <c r="P161" s="4" t="n"/>
       <c r="Q161" s="4" t="inlineStr">
         <is>
           <t>D0=58.92; 最新=2026-06-02; 相对D0=0.29%</t>
@@ -11625,24 +9240,6 @@
       <c r="J162" t="n">
         <v>13.82</v>
       </c>
-      <c r="K162" t="n">
-        <v/>
-      </c>
-      <c r="L162" t="n">
-        <v/>
-      </c>
-      <c r="M162" t="n">
-        <v/>
-      </c>
-      <c r="N162" t="n">
-        <v/>
-      </c>
-      <c r="O162" t="n">
-        <v/>
-      </c>
-      <c r="P162" t="n">
-        <v/>
-      </c>
       <c r="Q162" t="inlineStr">
         <is>
           <t>D0=13.89; 最新=2026-06-02; 相对D0=-0.50%</t>
@@ -11694,24 +9291,6 @@
       <c r="J163" t="n">
         <v>15.25</v>
       </c>
-      <c r="K163" t="n">
-        <v/>
-      </c>
-      <c r="L163" t="n">
-        <v/>
-      </c>
-      <c r="M163" t="n">
-        <v/>
-      </c>
-      <c r="N163" t="n">
-        <v/>
-      </c>
-      <c r="O163" t="n">
-        <v/>
-      </c>
-      <c r="P163" t="n">
-        <v/>
-      </c>
       <c r="Q163" t="inlineStr">
         <is>
           <t>D0=15.58; 最新=2026-06-02; 相对D0=-2.12%</t>
@@ -11763,24 +9342,12 @@
       <c r="J164" s="4" t="n">
         <v>19.52</v>
       </c>
-      <c r="K164" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L164" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M164" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N164" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O164" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P164" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K164" s="4" t="n"/>
+      <c r="L164" s="4" t="n"/>
+      <c r="M164" s="4" t="n"/>
+      <c r="N164" s="4" t="n"/>
+      <c r="O164" s="4" t="n"/>
+      <c r="P164" s="4" t="n"/>
       <c r="Q164" s="4" t="inlineStr">
         <is>
           <t>D0=17.62; 最新=2026-06-02; 相对D0=10.78%</t>
@@ -11832,24 +9399,6 @@
       <c r="J165" t="n">
         <v>334.5945</v>
       </c>
-      <c r="K165" t="n">
-        <v/>
-      </c>
-      <c r="L165" t="n">
-        <v/>
-      </c>
-      <c r="M165" t="n">
-        <v/>
-      </c>
-      <c r="N165" t="n">
-        <v/>
-      </c>
-      <c r="O165" t="n">
-        <v/>
-      </c>
-      <c r="P165" t="n">
-        <v/>
-      </c>
       <c r="Q165" t="inlineStr">
         <is>
           <t>D0=323.39; 最新=2026-06-02; 相对D0=3.46%</t>
@@ -11901,24 +9450,6 @@
       <c r="J166" t="n">
         <v>144.15</v>
       </c>
-      <c r="K166" t="n">
-        <v/>
-      </c>
-      <c r="L166" t="n">
-        <v/>
-      </c>
-      <c r="M166" t="n">
-        <v/>
-      </c>
-      <c r="N166" t="n">
-        <v/>
-      </c>
-      <c r="O166" t="n">
-        <v/>
-      </c>
-      <c r="P166" t="n">
-        <v/>
-      </c>
       <c r="Q166" t="inlineStr">
         <is>
           <t>D0=155.71; 最新=2026-06-02; 相对D0=-7.42%</t>
@@ -11969,24 +9500,6 @@
       </c>
       <c r="J167" t="n">
         <v>51.465</v>
-      </c>
-      <c r="K167" t="n">
-        <v/>
-      </c>
-      <c r="L167" t="n">
-        <v/>
-      </c>
-      <c r="M167" t="n">
-        <v/>
-      </c>
-      <c r="N167" t="n">
-        <v/>
-      </c>
-      <c r="O167" t="n">
-        <v/>
-      </c>
-      <c r="P167" t="n">
-        <v/>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
@@ -12224,24 +9737,12 @@
       <c r="J179" s="4" t="n">
         <v>40.12</v>
       </c>
-      <c r="K179" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L179" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M179" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N179" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O179" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P179" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K179" s="4" t="n"/>
+      <c r="L179" s="4" t="n"/>
+      <c r="M179" s="4" t="n"/>
+      <c r="N179" s="4" t="n"/>
+      <c r="O179" s="4" t="n"/>
+      <c r="P179" s="4" t="n"/>
       <c r="Q179" s="4" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-06-02; 相对D0=-3.26%</t>
@@ -12262,7 +9763,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -12289,24 +9789,6 @@
       <c r="J180" t="n">
         <v>89.92</v>
       </c>
-      <c r="K180" t="n">
-        <v/>
-      </c>
-      <c r="L180" t="n">
-        <v/>
-      </c>
-      <c r="M180" t="n">
-        <v/>
-      </c>
-      <c r="N180" t="n">
-        <v/>
-      </c>
-      <c r="O180" t="n">
-        <v/>
-      </c>
-      <c r="P180" t="n">
-        <v/>
-      </c>
       <c r="Q180" t="inlineStr">
         <is>
           <t>D0=90.64; 最新=2026-06-02; 相对D0=-0.79%</t>
@@ -12358,24 +9840,12 @@
       <c r="J181" s="4" t="n">
         <v>187.63</v>
       </c>
-      <c r="K181" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L181" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M181" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N181" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O181" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P181" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K181" s="4" t="n"/>
+      <c r="L181" s="4" t="n"/>
+      <c r="M181" s="4" t="n"/>
+      <c r="N181" s="4" t="n"/>
+      <c r="O181" s="4" t="n"/>
+      <c r="P181" s="4" t="n"/>
       <c r="Q181" s="4" t="inlineStr">
         <is>
           <t>D0=184.71; 最新=2026-06-02; 相对D0=1.58%</t>
@@ -12427,24 +9897,12 @@
       <c r="J182" s="4" t="n">
         <v>138.63</v>
       </c>
-      <c r="K182" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L182" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M182" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N182" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O182" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P182" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K182" s="4" t="n"/>
+      <c r="L182" s="4" t="n"/>
+      <c r="M182" s="4" t="n"/>
+      <c r="N182" s="4" t="n"/>
+      <c r="O182" s="4" t="n"/>
+      <c r="P182" s="4" t="n"/>
       <c r="Q182" s="4" t="inlineStr">
         <is>
           <t>D0=136.20; 最新=2026-06-02; 相对D0=1.78%</t>
@@ -12496,24 +9954,6 @@
       <c r="J183" t="n">
         <v>398.46</v>
       </c>
-      <c r="K183" t="n">
-        <v/>
-      </c>
-      <c r="L183" t="n">
-        <v/>
-      </c>
-      <c r="M183" t="n">
-        <v/>
-      </c>
-      <c r="N183" t="n">
-        <v/>
-      </c>
-      <c r="O183" t="n">
-        <v/>
-      </c>
-      <c r="P183" t="n">
-        <v/>
-      </c>
       <c r="Q183" t="inlineStr">
         <is>
           <t>D0=307.35; 最新=2026-06-02; 相对D0=29.64%</t>
@@ -12565,24 +10005,12 @@
       <c r="J184" s="4" t="n">
         <v>59.09</v>
       </c>
-      <c r="K184" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L184" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M184" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N184" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O184" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P184" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K184" s="4" t="n"/>
+      <c r="L184" s="4" t="n"/>
+      <c r="M184" s="4" t="n"/>
+      <c r="N184" s="4" t="n"/>
+      <c r="O184" s="4" t="n"/>
+      <c r="P184" s="4" t="n"/>
       <c r="Q184" s="4" t="inlineStr">
         <is>
           <t>D0=57.46; 最新=2026-06-02; 相对D0=2.84%</t>
@@ -12634,24 +10062,12 @@
       <c r="J185" s="4" t="n">
         <v>13.82</v>
       </c>
-      <c r="K185" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L185" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M185" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N185" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O185" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P185" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K185" s="4" t="n"/>
+      <c r="L185" s="4" t="n"/>
+      <c r="M185" s="4" t="n"/>
+      <c r="N185" s="4" t="n"/>
+      <c r="O185" s="4" t="n"/>
+      <c r="P185" s="4" t="n"/>
       <c r="Q185" s="4" t="inlineStr">
         <is>
           <t>D0=13.35; 最新=2026-06-02; 相对D0=3.52%</t>
@@ -12703,24 +10119,12 @@
       <c r="J186" s="4" t="n">
         <v>57.945</v>
       </c>
-      <c r="K186" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L186" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M186" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N186" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O186" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P186" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K186" s="4" t="n"/>
+      <c r="L186" s="4" t="n"/>
+      <c r="M186" s="4" t="n"/>
+      <c r="N186" s="4" t="n"/>
+      <c r="O186" s="4" t="n"/>
+      <c r="P186" s="4" t="n"/>
       <c r="Q186" s="4" t="inlineStr">
         <is>
           <t>D0=57.85; 最新=2026-06-02; 相对D0=0.16%</t>
@@ -12772,24 +10176,12 @@
       <c r="J187" s="4" t="n">
         <v>56.57</v>
       </c>
-      <c r="K187" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L187" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M187" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N187" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O187" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P187" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K187" s="4" t="n"/>
+      <c r="L187" s="4" t="n"/>
+      <c r="M187" s="4" t="n"/>
+      <c r="N187" s="4" t="n"/>
+      <c r="O187" s="4" t="n"/>
+      <c r="P187" s="4" t="n"/>
       <c r="Q187" s="4" t="inlineStr">
         <is>
           <t>D0=56.50; 最新=2026-06-02; 相对D0=0.12%</t>
@@ -12841,24 +10233,6 @@
       <c r="J188" t="n">
         <v>144.15</v>
       </c>
-      <c r="K188" t="n">
-        <v/>
-      </c>
-      <c r="L188" t="n">
-        <v/>
-      </c>
-      <c r="M188" t="n">
-        <v/>
-      </c>
-      <c r="N188" t="n">
-        <v/>
-      </c>
-      <c r="O188" t="n">
-        <v/>
-      </c>
-      <c r="P188" t="n">
-        <v/>
-      </c>
       <c r="Q188" t="inlineStr">
         <is>
           <t>D0=126.41; 最新=2026-06-02; 相对D0=14.03%</t>
@@ -12910,24 +10284,12 @@
       <c r="J189" s="4" t="n">
         <v>110.93</v>
       </c>
-      <c r="K189" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L189" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M189" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N189" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O189" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P189" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K189" s="4" t="n"/>
+      <c r="L189" s="4" t="n"/>
+      <c r="M189" s="4" t="n"/>
+      <c r="N189" s="4" t="n"/>
+      <c r="O189" s="4" t="n"/>
+      <c r="P189" s="4" t="n"/>
       <c r="Q189" s="4" t="inlineStr">
         <is>
           <t>D0=115.70; 最新=2026-06-02; 相对D0=-4.12%</t>
@@ -12979,24 +10341,6 @@
       <c r="J190" t="n">
         <v>272.65</v>
       </c>
-      <c r="K190" t="n">
-        <v/>
-      </c>
-      <c r="L190" t="n">
-        <v/>
-      </c>
-      <c r="M190" t="n">
-        <v/>
-      </c>
-      <c r="N190" t="n">
-        <v/>
-      </c>
-      <c r="O190" t="n">
-        <v/>
-      </c>
-      <c r="P190" t="n">
-        <v/>
-      </c>
       <c r="Q190" t="inlineStr">
         <is>
           <t>D0=286.31; 最新=2026-06-02; 相对D0=-4.77%</t>
@@ -13048,24 +10392,12 @@
       <c r="J191" s="4" t="n">
         <v>200.4</v>
       </c>
-      <c r="K191" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L191" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M191" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N191" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O191" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P191" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K191" s="4" t="n"/>
+      <c r="L191" s="4" t="n"/>
+      <c r="M191" s="4" t="n"/>
+      <c r="N191" s="4" t="n"/>
+      <c r="O191" s="4" t="n"/>
+      <c r="P191" s="4" t="n"/>
       <c r="Q191" s="4" t="inlineStr">
         <is>
           <t>D0=182.97; 最新=2026-06-02; 相对D0=9.53%</t>
@@ -13117,24 +10449,6 @@
       <c r="J192" t="n">
         <v>508.37</v>
       </c>
-      <c r="K192" t="n">
-        <v/>
-      </c>
-      <c r="L192" t="n">
-        <v/>
-      </c>
-      <c r="M192" t="n">
-        <v/>
-      </c>
-      <c r="N192" t="n">
-        <v/>
-      </c>
-      <c r="O192" t="n">
-        <v/>
-      </c>
-      <c r="P192" t="n">
-        <v/>
-      </c>
       <c r="Q192" t="inlineStr">
         <is>
           <t>D0=480.64; 最新=2026-06-02; 相对D0=5.77%</t>
@@ -13186,24 +10500,12 @@
       <c r="J193" s="4" t="n">
         <v>113</v>
       </c>
-      <c r="K193" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L193" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M193" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N193" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O193" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P193" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K193" s="4" t="n"/>
+      <c r="L193" s="4" t="n"/>
+      <c r="M193" s="4" t="n"/>
+      <c r="N193" s="4" t="n"/>
+      <c r="O193" s="4" t="n"/>
+      <c r="P193" s="4" t="n"/>
       <c r="Q193" s="4" t="inlineStr">
         <is>
           <t>D0=92.33; 最新=2026-06-02; 相对D0=22.39%</t>
@@ -13255,24 +10557,12 @@
       <c r="J194" s="4" t="n">
         <v>74.73999999999999</v>
       </c>
-      <c r="K194" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L194" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M194" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N194" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O194" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P194" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K194" s="4" t="n"/>
+      <c r="L194" s="4" t="n"/>
+      <c r="M194" s="4" t="n"/>
+      <c r="N194" s="4" t="n"/>
+      <c r="O194" s="4" t="n"/>
+      <c r="P194" s="4" t="n"/>
       <c r="Q194" s="4" t="inlineStr">
         <is>
           <t>D0=69.56; 最新=2026-06-02; 相对D0=7.45%</t>
@@ -13324,24 +10614,12 @@
       <c r="J195" s="4" t="n">
         <v>303.1</v>
       </c>
-      <c r="K195" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L195" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M195" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N195" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O195" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P195" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K195" s="4" t="n"/>
+      <c r="L195" s="4" t="n"/>
+      <c r="M195" s="4" t="n"/>
+      <c r="N195" s="4" t="n"/>
+      <c r="O195" s="4" t="n"/>
+      <c r="P195" s="4" t="n"/>
       <c r="Q195" s="4" t="inlineStr">
         <is>
           <t>D0=285.00; 最新=2026-06-02; 相对D0=6.35%</t>
@@ -13393,24 +10671,12 @@
       <c r="J196" s="4" t="n">
         <v>187.24</v>
       </c>
-      <c r="K196" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L196" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M196" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N196" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O196" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P196" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K196" s="4" t="n"/>
+      <c r="L196" s="4" t="n"/>
+      <c r="M196" s="4" t="n"/>
+      <c r="N196" s="4" t="n"/>
+      <c r="O196" s="4" t="n"/>
+      <c r="P196" s="4" t="n"/>
       <c r="Q196" s="4" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-02; 相对D0=9.08%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -13462,24 +10728,12 @@
       <c r="J197" s="4" t="n">
         <v>426.89</v>
       </c>
-      <c r="K197" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L197" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M197" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N197" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O197" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P197" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K197" s="4" t="n"/>
+      <c r="L197" s="4" t="n"/>
+      <c r="M197" s="4" t="n"/>
+      <c r="N197" s="4" t="n"/>
+      <c r="O197" s="4" t="n"/>
+      <c r="P197" s="4" t="n"/>
       <c r="Q197" s="4" t="inlineStr">
         <is>
           <t>D0=361.47; 最新=2026-06-02; 相对D0=18.10%</t>
@@ -13531,24 +10785,12 @@
       <c r="J198" s="4" t="n">
         <v>27.9</v>
       </c>
-      <c r="K198" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L198" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M198" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N198" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O198" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P198" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K198" s="4" t="n"/>
+      <c r="L198" s="4" t="n"/>
+      <c r="M198" s="4" t="n"/>
+      <c r="N198" s="4" t="n"/>
+      <c r="O198" s="4" t="n"/>
+      <c r="P198" s="4" t="n"/>
       <c r="Q198" s="4" t="inlineStr">
         <is>
           <t>D0=18.88; 最新=2026-06-02; 相对D0=47.78%</t>
@@ -13600,24 +10842,6 @@
       <c r="J199" t="n">
         <v>107.86</v>
       </c>
-      <c r="K199" t="n">
-        <v/>
-      </c>
-      <c r="L199" t="n">
-        <v/>
-      </c>
-      <c r="M199" t="n">
-        <v/>
-      </c>
-      <c r="N199" t="n">
-        <v/>
-      </c>
-      <c r="O199" t="n">
-        <v/>
-      </c>
-      <c r="P199" t="n">
-        <v/>
-      </c>
       <c r="Q199" t="inlineStr">
         <is>
           <t>D0=114.68; 最新=2026-06-02; 相对D0=-5.95%</t>
@@ -13669,24 +10893,12 @@
       <c r="J200" s="4" t="n">
         <v>133.52</v>
       </c>
-      <c r="K200" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L200" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M200" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N200" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O200" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P200" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K200" s="4" t="n"/>
+      <c r="L200" s="4" t="n"/>
+      <c r="M200" s="4" t="n"/>
+      <c r="N200" s="4" t="n"/>
+      <c r="O200" s="4" t="n"/>
+      <c r="P200" s="4" t="n"/>
       <c r="Q200" s="4" t="inlineStr">
         <is>
           <t>D0=134.08; 最新=2026-06-02; 相对D0=-0.42%</t>
@@ -13738,24 +10950,12 @@
       <c r="J201" s="4" t="n">
         <v>274.71</v>
       </c>
-      <c r="K201" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L201" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M201" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N201" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O201" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P201" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K201" s="4" t="n"/>
+      <c r="L201" s="4" t="n"/>
+      <c r="M201" s="4" t="n"/>
+      <c r="N201" s="4" t="n"/>
+      <c r="O201" s="4" t="n"/>
+      <c r="P201" s="4" t="n"/>
       <c r="Q201" s="4" t="inlineStr">
         <is>
           <t>D0=255.23; 最新=2026-06-02; 相对D0=7.63%</t>
@@ -13807,24 +11007,6 @@
       <c r="J202" t="n">
         <v>118.17</v>
       </c>
-      <c r="K202" t="n">
-        <v/>
-      </c>
-      <c r="L202" t="n">
-        <v/>
-      </c>
-      <c r="M202" t="n">
-        <v/>
-      </c>
-      <c r="N202" t="n">
-        <v/>
-      </c>
-      <c r="O202" t="n">
-        <v/>
-      </c>
-      <c r="P202" t="n">
-        <v/>
-      </c>
       <c r="Q202" t="inlineStr">
         <is>
           <t>D0=105.65; 最新=2026-06-02; 相对D0=11.85%</t>
@@ -13876,24 +11058,12 @@
       <c r="J203" s="4" t="n">
         <v>187.24</v>
       </c>
-      <c r="K203" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L203" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M203" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N203" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O203" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P203" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K203" s="4" t="n"/>
+      <c r="L203" s="4" t="n"/>
+      <c r="M203" s="4" t="n"/>
+      <c r="N203" s="4" t="n"/>
+      <c r="O203" s="4" t="n"/>
+      <c r="P203" s="4" t="n"/>
       <c r="Q203" s="4" t="inlineStr">
         <is>
           <t>D0=163.09; 最新=2026-06-02; 相对D0=14.81%</t>
@@ -13945,24 +11115,6 @@
       <c r="J204" t="n">
         <v>66.45</v>
       </c>
-      <c r="K204" t="n">
-        <v/>
-      </c>
-      <c r="L204" t="n">
-        <v/>
-      </c>
-      <c r="M204" t="n">
-        <v/>
-      </c>
-      <c r="N204" t="n">
-        <v/>
-      </c>
-      <c r="O204" t="n">
-        <v/>
-      </c>
-      <c r="P204" t="n">
-        <v/>
-      </c>
       <c r="Q204" t="inlineStr">
         <is>
           <t>D0=64.61; 最新=2026-06-02; 相对D0=2.85%</t>
@@ -14014,24 +11166,12 @@
       <c r="J205" s="4" t="n">
         <v>142.92</v>
       </c>
-      <c r="K205" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L205" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M205" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N205" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O205" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P205" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K205" s="4" t="n"/>
+      <c r="L205" s="4" t="n"/>
+      <c r="M205" s="4" t="n"/>
+      <c r="N205" s="4" t="n"/>
+      <c r="O205" s="4" t="n"/>
+      <c r="P205" s="4" t="n"/>
       <c r="Q205" s="4" t="inlineStr">
         <is>
           <t>D0=135.73; 最新=2026-06-02; 相对D0=5.30%</t>
@@ -14083,24 +11223,6 @@
       <c r="J206" t="n">
         <v>597.63</v>
       </c>
-      <c r="K206" t="n">
-        <v/>
-      </c>
-      <c r="L206" t="n">
-        <v/>
-      </c>
-      <c r="M206" t="n">
-        <v/>
-      </c>
-      <c r="N206" t="n">
-        <v/>
-      </c>
-      <c r="O206" t="n">
-        <v/>
-      </c>
-      <c r="P206" t="n">
-        <v/>
-      </c>
       <c r="Q206" t="inlineStr">
         <is>
           <t>D0=600.47; 最新=2026-06-02; 相对D0=-0.47%</t>
@@ -14152,24 +11274,12 @@
       <c r="J207" s="4" t="n">
         <v>25.86</v>
       </c>
-      <c r="K207" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L207" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M207" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N207" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O207" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P207" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K207" s="4" t="n"/>
+      <c r="L207" s="4" t="n"/>
+      <c r="M207" s="4" t="n"/>
+      <c r="N207" s="4" t="n"/>
+      <c r="O207" s="4" t="n"/>
+      <c r="P207" s="4" t="n"/>
       <c r="Q207" s="4" t="inlineStr">
         <is>
           <t>D0=24.86; 最新=2026-06-02; 相对D0=4.02%</t>
@@ -14220,24 +11330,6 @@
       </c>
       <c r="J208" t="n">
         <v>423.74</v>
-      </c>
-      <c r="K208" t="n">
-        <v/>
-      </c>
-      <c r="L208" t="n">
-        <v/>
-      </c>
-      <c r="M208" t="n">
-        <v/>
-      </c>
-      <c r="N208" t="n">
-        <v/>
-      </c>
-      <c r="O208" t="n">
-        <v/>
-      </c>
-      <c r="P208" t="n">
-        <v/>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
@@ -14335,7 +11427,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14347,7 +11438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -14955,7 +12046,6 @@
       <c r="M12" s="19" t="n">
         <v>0.039133</v>
       </c>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14984,7 +12074,6 @@
       <c r="F13" t="n">
         <v>290.01</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>285</v>
       </c>
@@ -15059,7 +12148,6 @@
       <c r="M14" s="17" t="n">
         <v>-0.012844</v>
       </c>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15088,7 +12176,6 @@
       <c r="F15" t="n">
         <v>67.38</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>66.94</v>
       </c>
@@ -15140,7 +12227,6 @@
       <c r="F16" t="n">
         <v>1069.4399</v>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>1068.04</v>
       </c>
@@ -15159,7 +12245,6 @@
       <c r="M16" s="19" t="n">
         <v>0.002085</v>
       </c>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -15673,9 +12758,7 @@
           <t>AXTI</t>
         </is>
       </c>
-      <c r="B35" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="20" t="n"/>
       <c r="C35" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -15721,9 +12804,7 @@
           <t>CEG</t>
         </is>
       </c>
-      <c r="B36" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="20" t="n"/>
       <c r="C36" s="4" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -15769,9 +12850,7 @@
           <t>GLW</t>
         </is>
       </c>
-      <c r="B37" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="20" t="n"/>
       <c r="C37" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -15817,9 +12896,7 @@
           <t>SNPS</t>
         </is>
       </c>
-      <c r="B38" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="20" t="n"/>
       <c r="C38" s="4" t="inlineStr">
         <is>
           <t>04 半导体设备 / EDA</t>
@@ -15923,9 +13000,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15937,7 +13011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -16184,7 +13258,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点</t>
+          <t>正式买入 | 第一观察点</t>
         </is>
       </c>
       <c r="F5" s="10" t="n">
@@ -16238,7 +13312,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F6" s="10" t="n">
@@ -16414,7 +13488,6 @@
       <c r="F9" t="n">
         <v>190.96</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>203.7</v>
       </c>
@@ -16439,7 +13512,6 @@
       <c r="O9" s="19" t="n">
         <v>0.280593</v>
       </c>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16468,7 +13540,6 @@
       <c r="F10" t="n">
         <v>90.87</v>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>91.09</v>
       </c>
@@ -16613,7 +13684,6 @@
       <c r="O12" s="19" t="n">
         <v>0.041665</v>
       </c>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -16913,9 +13983,7 @@
           <t>SLB</t>
         </is>
       </c>
-      <c r="B26" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B26" s="20" t="n"/>
       <c r="C26" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -16967,9 +14035,7 @@
           <t>ZS</t>
         </is>
       </c>
-      <c r="B27" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B27" s="20" t="n"/>
       <c r="C27" s="4" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -17066,10 +14132,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17081,7 +14143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R56"/>
+  <dimension ref="A1:R54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -17480,7 +14542,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F7" s="10" t="n">
@@ -17610,7 +14672,6 @@
       <c r="F9" t="n">
         <v>105.89</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>104.27</v>
       </c>
@@ -18680,7 +15741,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -18721,7 +15782,6 @@
       <c r="Q26" s="19" t="n">
         <v>0.030283</v>
       </c>
-      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -18744,7 +15804,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
@@ -18864,7 +15924,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
@@ -19103,9 +16163,7 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="B41" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="20" t="n"/>
       <c r="C41" s="4" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -19163,9 +16221,7 @@
           <t>CVX</t>
         </is>
       </c>
-      <c r="B42" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="20" t="n"/>
       <c r="C42" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -19223,9 +16279,7 @@
           <t>EOG</t>
         </is>
       </c>
-      <c r="B43" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B43" s="20" t="n"/>
       <c r="C43" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -19283,9 +16337,7 @@
           <t>MDB</t>
         </is>
       </c>
-      <c r="B44" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B44" s="20" t="n"/>
       <c r="C44" s="4" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -19343,9 +16395,7 @@
           <t>OXY</t>
         </is>
       </c>
-      <c r="B45" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="20" t="n"/>
       <c r="C45" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -19403,9 +16453,7 @@
           <t>POET</t>
         </is>
       </c>
-      <c r="B46" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B46" s="20" t="n"/>
       <c r="C46" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -19463,9 +16511,7 @@
           <t>XLE</t>
         </is>
       </c>
-      <c r="B47" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B47" s="20" t="n"/>
       <c r="C47" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -19594,8 +16640,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19607,7 +16651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -19768,24 +16812,12 @@
       <c r="J3" s="4" t="n">
         <v>181.49</v>
       </c>
-      <c r="K3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19837,24 +16869,12 @@
       <c r="J4" s="4" t="n">
         <v>202.91</v>
       </c>
-      <c r="K4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19906,24 +16926,12 @@
       <c r="J5" s="4" t="n">
         <v>167.37</v>
       </c>
-      <c r="K5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19975,24 +16983,12 @@
       <c r="J6" s="4" t="n">
         <v>46.53</v>
       </c>
-      <c r="K6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20044,24 +17040,6 @@
       <c r="J7" t="n">
         <v>16.12</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20113,24 +17091,12 @@
       <c r="J8" s="4" t="n">
         <v>180.07</v>
       </c>
-      <c r="K8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20182,24 +17148,12 @@
       <c r="J9" s="4" t="n">
         <v>48.12</v>
       </c>
-      <c r="K9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20251,24 +17205,6 @@
       <c r="J10" t="n">
         <v>141.22</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20320,24 +17256,12 @@
       <c r="J11" s="4" t="n">
         <v>391.35</v>
       </c>
-      <c r="K11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20389,24 +17313,12 @@
       <c r="J12" s="4" t="n">
         <v>1038.74</v>
       </c>
-      <c r="K12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
+      <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20458,24 +17370,12 @@
       <c r="J13" s="4" t="n">
         <v>179.36</v>
       </c>
-      <c r="K13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20527,24 +17427,12 @@
       <c r="J14" s="4" t="n">
         <v>326.13</v>
       </c>
-      <c r="K14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20596,24 +17484,6 @@
       <c r="J15" t="n">
         <v>22.51</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20665,24 +17535,6 @@
       <c r="J16" t="n">
         <v>232</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20734,24 +17586,6 @@
       <c r="J17" t="n">
         <v>130.5</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20803,24 +17637,12 @@
       <c r="J18" s="4" t="n">
         <v>262.25</v>
       </c>
-      <c r="K18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20872,24 +17694,12 @@
       <c r="J19" s="4" t="n">
         <v>85.42</v>
       </c>
-      <c r="K19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20941,24 +17751,6 @@
       <c r="J20" t="n">
         <v>426.01</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -21010,24 +17802,12 @@
       <c r="J21" s="4" t="n">
         <v>13.02</v>
       </c>
-      <c r="K21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -21264,24 +18044,12 @@
       <c r="J33" s="4" t="n">
         <v>41.47</v>
       </c>
-      <c r="K33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -21326,11 +18094,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21342,7 +18105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T54"/>
+  <dimension ref="A1:T49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -21503,7 +18266,6 @@
       <c r="F3" t="n">
         <v>22.51</v>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>22.62</v>
       </c>
@@ -21923,7 +18685,6 @@
       <c r="F9" t="n">
         <v>181.49</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>177.62</v>
       </c>
@@ -22339,7 +19100,6 @@
       <c r="F15" t="n">
         <v>16.12</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>15.47</v>
       </c>
@@ -22479,7 +19239,6 @@
       <c r="F17" t="n">
         <v>610.26</v>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>612.34</v>
       </c>
@@ -22825,7 +19584,6 @@
       <c r="F22" t="n">
         <v>141.22</v>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>136.2</v>
       </c>
@@ -22895,7 +19653,6 @@
       <c r="F23" t="n">
         <v>58.81</v>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>57.46</v>
       </c>
@@ -22965,7 +19722,6 @@
       <c r="F24" t="n">
         <v>81.76000000000001</v>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>84.64</v>
       </c>
@@ -23029,7 +19785,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
@@ -23105,7 +19861,6 @@
       <c r="F26" t="n">
         <v>426.01</v>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>433.59</v>
       </c>
@@ -23142,7 +19897,6 @@
       <c r="S26" s="17" t="n">
         <v>-0.005329</v>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -23165,7 +19919,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
@@ -23445,7 +20199,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
@@ -23515,7 +20269,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
@@ -23832,9 +20586,7 @@
           <t>HAL</t>
         </is>
       </c>
-      <c r="B45" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="20" t="n"/>
       <c r="C45" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -23930,11 +20682,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25136,8 +21883,6 @@
       <c r="T13" t="b">
         <v>0</v>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="n">
         <v>90</v>
       </c>
@@ -25318,7 +22063,6 @@
       <c r="V15" t="n">
         <v>245.9499053955078</v>
       </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=62.28; 4H分金=60.18</t>
@@ -26480,8 +23224,6 @@
       <c r="T28" t="b">
         <v>0</v>
       </c>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
       <c r="W28" t="n">
         <v>87</v>
       </c>
@@ -27106,8 +23848,6 @@
       <c r="T35" t="b">
         <v>0</v>
       </c>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
       <c r="W35" t="n">
         <v>96</v>
       </c>
@@ -28676,7 +25416,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -28946,7 +25686,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -29516,7 +26256,6 @@
           <t>19 COWOS</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" s="8" t="n">
         <v>46164</v>
       </c>
@@ -29625,7 +26364,6 @@
       <c r="D4" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="8" t="n">
         <v>46164</v>
       </c>
@@ -29785,7 +26523,6 @@
       <c r="D7" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="8" t="n">
         <v>46164</v>
       </c>
@@ -30504,7 +27241,6 @@
       <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" s="8" t="n">
         <v>46175</v>
       </c>
@@ -31186,7 +27922,6 @@
       <c r="I23" t="n">
         <v>3</v>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" s="8" t="n">
         <v>46171</v>
       </c>
@@ -31298,7 +28033,6 @@
       <c r="I25" t="n">
         <v>5</v>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" s="8" t="n">
         <v>46169</v>
       </c>
@@ -31526,7 +28260,6 @@
           <t>2026-05-22 (100), 2026-05-26 (80)</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -31617,7 +28350,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F9" s="10" t="n">
@@ -31651,7 +28384,7 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F10" s="10" t="n">
@@ -31685,7 +28418,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点</t>
+          <t>正式买入 | 第一观察点</t>
         </is>
       </c>
       <c r="F11" s="10" t="n">
@@ -32370,7 +29103,6 @@
           <t>2026-05-22 (88), 2026-05-26 (93)</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -32468,7 +29200,6 @@
           <t>2026-05-22 (91), 2026-05-26 (88)</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -32502,7 +29233,6 @@
           <t>2026-05-22 (86), 2026-05-26 (87)</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -32595,8 +29325,6 @@
       <c r="F39" t="n">
         <v>315.2</v>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -32625,8 +29353,6 @@
       <c r="F40" t="n">
         <v>72.33</v>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -32655,8 +29381,6 @@
       <c r="F41" t="n">
         <v>11.7</v>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42"/>
     <row r="43">
@@ -32811,7 +29535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -32906,7 +29630,7 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F3" s="10" t="n">
@@ -33100,14 +29824,12 @@
       <c r="F8" t="n">
         <v>69.56999999999999</v>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>68.5</v>
       </c>
       <c r="I8" s="17" t="n">
         <v>-0.01538</v>
       </c>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -33212,14 +29934,12 @@
       <c r="F11" t="n">
         <v>14.7</v>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>14.7</v>
       </c>
       <c r="I11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -33328,14 +30048,12 @@
       <c r="F14" t="n">
         <v>15.58</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>15.25</v>
       </c>
       <c r="I14" s="17" t="n">
         <v>-0.021181</v>
       </c>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -33455,7 +30173,6 @@
       <c r="I17" s="19" t="n">
         <v>0.034647</v>
       </c>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -33885,9 +30602,7 @@
           <t>ASTS</t>
         </is>
       </c>
-      <c r="B36" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="20" t="n"/>
       <c r="C36" s="4" t="inlineStr">
         <is>
           <t>17 高弹性交易池</t>
@@ -33921,9 +30636,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B37" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="20" t="n"/>
       <c r="C37" s="4" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -33961,9 +30674,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B38" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="20" t="n"/>
       <c r="C38" s="4" t="inlineStr">
         <is>
           <t>15 公用事业</t>
@@ -33997,9 +30708,7 @@
           <t>ENTG</t>
         </is>
       </c>
-      <c r="B39" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B39" s="20" t="n"/>
       <c r="C39" s="4" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -34033,9 +30742,7 @@
           <t>META</t>
         </is>
       </c>
-      <c r="B40" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B40" s="20" t="n"/>
       <c r="C40" s="4" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -34069,9 +30776,7 @@
           <t>NVTS</t>
         </is>
       </c>
-      <c r="B41" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="20" t="n"/>
       <c r="C41" s="4" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -34105,9 +30810,7 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B42" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="20" t="n"/>
       <c r="C42" s="4" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -34225,7 +30928,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -34237,7 +30939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -34478,7 +31180,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>买入跟踪 | 正式买入 | 第一买入点 | 预警买入</t>
+          <t>买入跟踪 | 正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F6" s="10" t="n">
@@ -34727,7 +31429,6 @@
       <c r="K11" s="19" t="n">
         <v>0.088925</v>
       </c>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -34894,7 +31595,6 @@
       <c r="F15" t="n">
         <v>1921.71</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>1940.04</v>
       </c>
@@ -34907,7 +31607,6 @@
       <c r="K15" s="19" t="n">
         <v>0.06426</v>
       </c>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16"/>
     <row r="17">
@@ -35075,9 +31774,7 @@
           <t>AEHR</t>
         </is>
       </c>
-      <c r="B27" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B27" s="20" t="n"/>
       <c r="C27" s="4" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -35117,9 +31814,7 @@
           <t>AMKR</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B28" s="20" t="n"/>
       <c r="C28" s="4" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -35159,9 +31854,7 @@
           <t>BE</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B29" s="20" t="n"/>
       <c r="C29" s="4" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -35201,9 +31894,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B30" s="20" t="n"/>
       <c r="C30" s="4" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -35247,9 +31938,7 @@
           <t>COHR</t>
         </is>
       </c>
-      <c r="B31" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B31" s="20" t="n"/>
       <c r="C31" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -35289,9 +31978,7 @@
           <t>FLNC</t>
         </is>
       </c>
-      <c r="B32" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B32" s="20" t="n"/>
       <c r="C32" s="4" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -35331,9 +32018,7 @@
           <t>INTC</t>
         </is>
       </c>
-      <c r="B33" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="20" t="n"/>
       <c r="C33" s="4" t="inlineStr">
         <is>
           <t>03 GPU / AI芯片</t>
@@ -35373,9 +32058,7 @@
           <t>NRG</t>
         </is>
       </c>
-      <c r="B34" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B34" s="20" t="n"/>
       <c r="C34" s="4" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -35415,9 +32098,7 @@
           <t>TSEM</t>
         </is>
       </c>
-      <c r="B35" s="20" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="20" t="n"/>
       <c r="C35" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -35541,7 +32222,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
